--- a/Indeed_US_CA_2026-05-08.xlsx
+++ b/Indeed_US_CA_2026-05-08.xlsx
@@ -397,1685 +397,1791 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I61"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="57.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="48.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="41.83203125" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B1" t="str">
         <v>Title</v>
       </c>
-      <c r="B1" t="str">
-        <v>Company</v>
-      </c>
       <c r="C1" t="str">
+        <v>Link</v>
+      </c>
+      <c r="D1" t="str">
         <v>Salary</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Location</v>
       </c>
-      <c r="E1" t="str">
-        <v>Apply Method</v>
-      </c>
       <c r="F1" t="str">
-        <v>Link</v>
+        <v>Page</v>
       </c>
       <c r="G1" t="str">
-        <v>Keyword</v>
+        <v>EasilyApply</v>
       </c>
       <c r="H1" t="str">
-        <v>Region</v>
+        <v>DateCrawled</v>
+      </c>
+      <c r="I1" t="str">
+        <v>CrawledBy</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Data Science Consultant</v>
+        <v>National Polytechnic College</v>
       </c>
       <c r="B2" t="str">
-        <v>Deloitte</v>
+        <v>Career Services Business Analyst</v>
       </c>
       <c r="C2" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0BV-MrnRv0S7fEuAE7zM1ZH__hGHxiXZzCyX8bdj55DKgV5X9M3hkGopXnGXua_NJ1S8_K36kigi8EIq0fG6AxaRp2QsrOFx-5YuQ_a5JGGwCw6CPggc7Zcld3XtiZZ91_aWLOPS58r_3F3emKa7wMmIa4CrtPq74IsTdOderSxOmt_zh7p8gcajD1jfVt15aAmpYWRSntkRJsAuxEBxc9MO8uNwHXn6xCcDQAelWOebz7XVqucTGBUDWN0OAtLEMJvwDl-qNIe42zoRZ9GITXx7XeUKZh8kbiRkLymzdLl7SgexRreM1DQrzXEZuQlI8x50DPIkvU1hFwyOlNcjS7BvgxKex-y7R4TR3SU3I8bgEqhtscaEJWTZwi98Wq-augs3rHK_JazgqJtjjtoZpaKqXkYkaGtD4mgD4v-BbnYyQzJ06JBqAviSmMAuFtoVX-H6pPNIacWGiukvxbDW11z-TJYB_xO4ZXHkPL3_tdmJPuovtSTP15mehuotUSZpWm_eWv6cv5UIBKG2adGvj6HbpyvvVmfCpPqIzC_ywceQzv_svLJm9Gne7YKctbCa0281ROLZdHPTOy1kEmDYzHVcqzTNbULi2VgqPcdk9-yMyisCHM2CPoFQZtxp7HBMllD4ciHpZ-ZwTZVBHOTVnu_NjmIueKy8kZNeE9e5mcdz1mhbj7m--V9RFkhm2aI234cY349x3TxIQ4BjjkqdUWL625whYYMXbPZXcqke_ieGg==&amp;xkcb=SoAq6_M3jDeTCByJzh0LbzkdCdPP&amp;camk=C3EPSzFlQw9rav0EeVD8wg==&amp;p=0&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D2" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
+        <v>$21 - $25 an hour</v>
       </c>
       <c r="E2" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=65b87289e914b8ad&amp;bb=7CMKH5B_VZ3BKSh5duqStGqqT3vzOcN2N42ceaiPT1ncy2OviKWSUxoT2Zta0CVvx9AhbXyCeSJeWvPaTf4MamNAOQjOhKGF-bovgefKUYmoHqYRY1XBPXIKcpCR14mL&amp;xkcb=SoCg67M3jDaggQQHYJ0LbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Lakewood, CA 90714</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H2" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GCP Cloud Analytics Engineer - Senior Consultant</v>
+        <v>Ubank Lending</v>
       </c>
       <c r="B3" t="str">
-        <v>Deloitte</v>
+        <v>Marketing Specialist</v>
       </c>
       <c r="C3" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0BHBIh4UjvqMyQOZeMl3b2fr1wllOCHEoWkwlDHHFoU--0eQQV-mBNXq69quSePqC-tyMs4HfwIiAgqj2wTFf0vSP84Na3qB-xSqqv8ekynRWaa957q6_W04uVJXxglYJ3hPj9tdCH5jUHizuYYAjV3JUV7nzyqD5hltPvKmqbp4WDkNwYaFQb5GpDYpQ7nH8F3Tk4r_FcRBdF-xxBdr1wGoFQ58ymyYWZjvoLgxGErkA8vPz3H-IHmFAIu6BeCYCFcINETWXXEolJj8qlEyTXKFTtzqyL_dxGj0Op-iosgP-cJ4jQ9hPTNUozcRpp_QLK8gYjGDPf7IGm-OsWwmfTaQQq6l91Jo7cFCsRIO1JFOaQdVTlxQYfeXxD4EYD8BqWQ4nRBaR_xTNgetLksfY1nrwVrzVfu-koADAfXE51x0jHxt-bdaiquhhJMEoP9xu9XKap58EdDRrw01rCoP18EIwj2uC4WPBqtI5ZNBviPOfziffQ7vE3kLmzuHsJnpNR86GLoCrUOiyncByPUD-Z5DifraBHX1PVee0Kn1V23DXAQbwzBqbWmrLqotToANg6S9J5l_UctnEU5tzcei8ZFsUBz-KlDwAZOBDtUo0GUtwfjjGBd8LSI2325yLt_RxUvO2sJgslGO5vNosOasT2wcC66wZN1QyXL69RvrPk0UrfRf2l85yhzPYt-94y6qsah3ZHkFrQmkJwM4-9mzGvwskowMZmBq9U=&amp;xkcb=SoCe6_M3jDeTCByJzh0KbzkdCdPP&amp;camk=C3EPSzFlQw9QOMuS8AgzmA==&amp;p=1&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D3" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
+        <v>$48,000 - $60,000 a year</v>
       </c>
       <c r="E3" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F3" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=2c314e6df20a4157&amp;bb=7CMKH5B_VZ3BKSh5duqStIkZJGFL7YDlJaaa8vxcEh6dgdjaVBCM3nB1o0QpE3pq4lomb7lv_hSZoF8Do4AwuznrWwzyHo_j06OpQpbrpPdcy8mZUopz3N_-k14HqOMM&amp;xkcb=SoAU67M3jDaggQQHYJ0KbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>City of Industry, CA 91748</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H3" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</v>
+        <v>Phynite</v>
       </c>
       <c r="B4" t="str">
-        <v>Deloitte</v>
+        <v>Luxury Specialist Reviewer</v>
       </c>
       <c r="C4" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0AqOxdqHwhfLcPjTsGyTljsyb11E0-g-QanTXOZjx3oEZoUA9Jm8Ij3n0gI9xj4tsN9JbtQRRCWY-l8iyQ8_CNgsEX2b_MG91GysQVmYNsUNgAxtaMVZdl2-Hro9gjmIIWQasoIdfCCUjuxz48v4ajeUppCaBIvrBXs_A2oSFU6l-UWGKHyxkM3iqdBuuCyWbcCyIqsHRi80KQa6RSPM9FyYxzshQNd1wSQ_mqt47-IJ8T6He0eb7zb-sVXZAE8biGxLkR-S7FVV6IIUFLGFQKNe4qWYC2-I1Ka16HGe71bC43Xiijo0GSFktbCxfRY5UmE_UbaiekBBdYky4M2zRcazkTOTZ7oF2yiNhmxsZDdayKifVIUdvdiyH1BEj2sJHWgmZlOUhGu-1SISZm-bfGjuQy1FM1jbM5UkNl-X1HGz-RSR--GfzZrXMPOvuA6m-LLQcgOWDm7PNkQOdIDkGmkl9Krk9DTRBRYd_MuIPxOMUSjtAtBm6UhFdxYD11rEDe3-IuzSR0XuSw1SGEmltRRjbfSGsyr0lrLqO4emlGyv5hFI_4wh4TUkqlCxRZgNaXgIbHG3J9bqSYeKZjV2AADKoAZ0f3mBi4-WTNl6O4ernDNURivv7oIEYAfHkTQjY1XeHGaQxOsWHV2eyDiAi4sGC-D_QJ-Xy2BrZh17oK03OF4tL7pEKR49UH_A8q0HpWnuzpXuByavQbD6_5NJf2s2-DlqnmIXH0=&amp;xkcb=SoAD6_M3jDeTCByJzh0JbzkdCdPP&amp;camk=C3EPSzFlQw-g2OuqrOZhOA==&amp;p=2&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D4" t="str">
-        <v>Costa Mesa, CA 92626</v>
+        <v>$18 - $20 an hour</v>
       </c>
       <c r="E4" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F4" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=f5808657aeae8aab&amp;bb=7CMKH5B_VZ3BKSh5duqStCg-9un9eXxYD3Oi4erSk5ZUGLlnvFY3mvltPpgmSedGyH7RYWWUda4jngM0Q8xdZ-NTPfOAQ29NpVD3N8ciMfL7pwcX4HnPviEPEQyYbKzX&amp;xkcb=SoCJ67M3jDaggQQHYJ0JbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Marina del Rey, CA 90292</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H4" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Workday Reporting Lead Consultant</v>
+        <v>Motion Picture Industry Pension &amp; Health Plans</v>
       </c>
       <c r="B5" t="str">
-        <v>Deloitte</v>
+        <v>Senior Analytics Engineer</v>
       </c>
       <c r="C5" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0Df2ZXQkQrVei7QMlJKqQnhPMfkXmZ2JHFrtIKPrV0FiquWsAcnFNwuvWC7nbkSY9PLqWE-SYcyB_Odk9fTsc2BUApWOJwPVTdP_dVRvZrOf3qzO3dvtcUepBTgJSFwLxRBxTDD-njfv7-ANCKGFp_iwejMC1Y60diVcpOTiAWx-HgGpFAFtCSMkFTsL7-9B9p0kG-GrOyr42Yc3y0oiry396CnC7ew1U2mkzI78LprHF78URqFzK0LXe92MoyPTafQmJe2N7WsBkuqdfT91AAAg1a3ZPp_M3lS-qZwFhl4tunySCFGFH1tcjTcb51wE58VH7bw7TcpcpxoAgoVKuFdq5XBQlbkbV3jn5VuXWzRiWIzG-QdXThdd4oyzcblsAJHGExCpNO2UGsq5BZPCLp9oWB2b6mxsAdbC44ZDU2NEUo4anKCiucSvOq9VVIXCMlhwzq1gAXNbfflEPgmZZNb0-NJC5BA0fuRwmsZ9zvXscXoC3sOmE10FhrtNbYnapOBzzgFuIaeWV_uFFHmyZAtFinI2bprQRPfQFMHXXhiirYErSl3s6OPB5Tfdpx8nNZ7aHIC_jkLOMRfrXnkLRv5WYEyGCrK47IcQUq-bVt87mxgkb4NxUXWwuLDrsTFHTQET6Q0uED4vKBXhUA9pdQihBhIpisQ_spbFfRnqMJ5hk60PhSw_Har&amp;xkcb=SoC36_M3jDeTCByJzh0IbzkdCdPP&amp;camk=UoKtGZLa3XLYYlMGlXSz5g==&amp;p=3&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D5" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
+        <v>$125,000 - $145,000 a year</v>
       </c>
       <c r="E5" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F5" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=73a2cb8df3c9dfec&amp;bb=7CMKH5B_VZ3BKSh5duqStICx9YVTBNL0t0QoedWWugUrsCI8KnaASzPJKi0dQSoN2pmlsszIFPLSOQIMlsSFoOhFNQZeEOaK3QSL-z_J0qo36GovAtqyw5OtDcE-MS_0&amp;xkcb=SoA967M3jDaggQQHYJ0IbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Hybrid work in Los Angeles, CA</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H5" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Oracle Technical Cloud Senior Consultant</v>
+        <v>FHA Review, Inc.</v>
       </c>
       <c r="B6" t="str">
-        <v>Deloitte</v>
+        <v>CONDO PROJECT ANALYST</v>
       </c>
       <c r="C6" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0Bc2jlze9sxox2Ht00jkZgUSUVF6nzEaaQ7MUfehUvywIy7R2PxiehNFs_x_0NielUeM9NKw_TN1-xgpnV1KVBlExaIQT8Nl7wJX7WDzc7bnnSpjpqgdYCvu0ZcX47g-w4oQdBNAihVQl7-cZq1Q1DX21HEjDhrKyB_9YSZeJoXrHNHE7uWOE0NiPGjb2CIMEUtXoVr9nuiKjJdQ56NJ1y1PivJ4VfokjM9x2Cmqk1KD7Q-Uzkkbre_7NGTObu2gmGNQfhdHCgWzzTrMglIfXE5dTtvrmhe1rIDy1MDejkKozSkhO-RWp_J6llfui2kPdJ_EExL30-PS1-nCI8Krc4HRU_VfjNCgcHpAcDqPAB-zI0Ikm-TkTLyrCvmetu8K5Mjp1wcASuTxe3v7a_TtdfN4gptjGx47ahZpMs-fqW6-F6_59AEANq90WMWK-4NLkT8zc8wcKycXeH5KAKTTYQUXTAmBYAKdOU3OVFdCH8odtMNs5ZZyJDu1mXmEpVNIz2DgDBsRgsqXgu82SW_rcmNNYi4P_8Iv1ATc8gKXaCqVp0c5BU6Kx8J99eurUInjG7sFELe7Cj-PCUP1V4T3eHHQFNm7kbqeKpvEUsQ1wiLCYtzAKGt9NMFsKyyZlEY6bIEFv-PlpkrFfaTZFHwHXT5I7zSOvaelHQQFrjr_vZ7FUEMhb6q5oJWIcVN30F9tk_upVAB040KTA==&amp;xkcb=SoA56_M3jDeTCByJzh0PbzkdCdPP&amp;camk=C3EPSzFlQw8VX7XQDzB5KQ==&amp;p=4&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D6" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
+        <v>$30 - $35 an hour</v>
       </c>
       <c r="E6" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=fc5cf84bf123b349&amp;bb=7CMKH5B_VZ3BKSh5duqStL26ppcEhU1DU6pF5KiKSbw96uU7YJ3WNSSNIzcCMB2WF7jYewOLW2fwG_UxBN5Rd7lNHxwWyoaCY5m1EvB8cU-4odlU_k5mJs6LYC-1Eg6k&amp;xkcb=SoCz67M3jDaggQQHYJ0PbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Hybrid work in Huntington Beach, CA 92648</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H6" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>E Mortgage Capital, Inc.</v>
+      </c>
+      <c r="B7" t="str">
         <v>Senior Data Analyst</v>
       </c>
-      <c r="B7" t="str">
-        <v>E Mortgage Capital, Inc.</v>
-      </c>
       <c r="C7" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0C_fRSquGjzmNO6l3MBXOc2vNlh1AIfO6oDydPsq-NnKKZcoKzdoZX2KnxSd1A6xAV7nUFwO_coUvZJ5mYhI8FnPLWB2GmhkHL2hi9KV3LmnyTvLbD-IKz3BOaxbR1fHGjwxI5AF84Xyr_yIHOK8Z-10_jO7ZhinITUM_sIZZUOQc9TEeC_58iNQQ7pHmBv7pNWDYTvXQsk61SOF1TS0fiEZmBIIDSSpp-u5aB_Kr-_9i2eX2uGjLPvkP75svn17iHDevr2B4C46S_agjVxx81H9NlejV381dlNY62IP0VEZCsp5IF9jwgI51aAQRwKsM7fHL98e-1KilAcs3MEaGnvTj1-jQyxzK2MkYrCfubdZvTrCEvUG5hBxaLkCzDKUfVjZ_ocewM72u37aCdUbt6QiuJ7xGADgFgBHUx9694XUgO02Rujt9QrTViUTP8JJh5YHKloMs4NKat2fVyJPD25FvLgfZ165DQa7kizx0yq24fMMAWPeuipYlNeHOa6q13upMwOnuLZUPI2Nsy0BDjDJJCMu7MOYFU1H_Z33r5r8aMWmbE3eOnIs5xxu_mVWSqieTzbuDAgm9NY5L5BnD7_mw3RE-3wh93kkf6ZqIxFiF5BcwVJT5LHb68WO1ieRszYxeTIQzkjwlqiYllxu5kfmpAN9cGi_VT1Mu7bazPCu_5ne5hayZ7Lxo0JVWL23EA=&amp;xkcb=SoCN6_M3jDeTCByJzh0ObzkdCdPP&amp;camk=C3EPSzFlQw_7KHwieZPDtA==&amp;p=5&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D7" t="str">
+        <v>$86,963.95 - $104,730.78 a year</v>
+      </c>
+      <c r="E7" t="str">
         <v>Santa Ana, CA 92704</v>
       </c>
-      <c r="E7" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F7" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0C_fRSquGjzmNO6l3MBXOc2vNlh1AIfO6oDydPsq-NnKKZcoKzdoZX2KnxSd1A6xAV7nUFwO_coUvZJ5mYhI8FnPLWB2GmhkHL2hi9KV3LmnyTvLbD-IKz3BOaxbR1fHGjwxI5AF84Xyr_yIHOK8Z-10_jO7ZhinITUM_sIZZUOQc9TEeC_58iNQQ7pHmBv7pNWDYTvXQsk68MoHmuadEvzuIBYdF9gw2H9c51cgSeizjmvyZb3bbZT0WtfszIqjY7Jg4r7lU1MXb9NLG29t7jNoIipRWREmtwssDg0K7mYmyDy4h_pJBnmr3gslBKlercAFLonvWzm02mTNS_D849ocnSuWsZOEHOQnzb3fPAWR5j2f_Y85NDWFOehhnB8Y5mVEJGQuM1pLIZ-6ZLbZBZ7G4yISfQLdbVtxhmEmk0ihBGpgTeN0cGdV6zm7eUtGXN64IWF3XjOXWzimlIynZEPrehJrqIUg001Y7WHLKkEIgMbG10KJ5n7E2fU6xjdNXS1twP2S804_mjK-phEmYuQCyxHLkEPrCGxTvV_vK5u1lec6JAoQMAyulO43wOOpELiLtBIPFEZIIV29sM35l3Y5_ET6T84JIHWIn56v9ZnxcDib4y_FrgU665mGZqMq30ooDRzkxx0mnvAv5r4zVBAgDB4dDgMubBRTcfMG3ctaN0s8BkTslkS7RSnViw0prc=&amp;xkcb=SoDz6_M3jDaggQQHYJ0ObzkdCdPP&amp;camk=C3EPSzFlQw_7KHwieZPDtA==&amp;p=5&amp;fvj=0&amp;vjs=3</v>
+      <c r="F7">
+        <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H7" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>J.P. Morgan Advisors - Business Analyst - Los Angeles, CA</v>
+        <v>Century Group International Inc</v>
       </c>
       <c r="B8" t="str">
-        <v>JPMorganChase</v>
+        <v>Data Analyst</v>
       </c>
       <c r="C8" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0Axl0MwAmnlUFatGrWDSgjR4egKJ2jBiTmnXOou2KtzDJLsHA5QVfeeFwGnYKgkB92dyL3VcvXF8TrTZR-w8k8_fWaGtYSD-TeiS27RrlQTEmJUvz7JMcd3CtxI4a9WG-mBbSd72CF9nzY5P-RY71FnaFr2tMD7WytWnawNspzttwawYvQRD7lb8uwz5ua8WlQm7z7_sF1cxSiqz453Y2bgLkJTNZ3CsgU0Dc5JBnXh74X5n-pdBxVkBudIejrWfudAiNHfIJoYgWH0zKGB14EZr5fYI5ReQ1lXGJhAs-b_5USLsX1IRkidofkkxSYlwkKRKGFVcxjOjSKNIrDjpa6a7tr2IgVsoa1DhYTP2vFcoeCzfn47RgJsD2aYinG2kUdoQwsZKTeAaY2ke2Ej0SxuhRUSgW0J73__nxJwsneBwam7lhtfGGCw7ziwIozNb8UhQWXiIyi1xeTp_nzPv_zaoh68VztrGXPGdBa8NAC5Q6zGL8YqpOGWD1awr-HIibR7UKNgAxMBhhARcKRQFrI1Ja2HWkMSRtWiDnk6anty_jWDQpltQNEZOP2qfkl5OUtBnU1di_v5BjfsDmtIlLTU1dG0pfEvK_IHzKfyPXjuTlLtY4EmpEBMiggpI0qb8iB9coGH9_25QcHCDVuIDhOpW1nFAqS4BLaryuSXFek4CA==&amp;xkcb=SoAQ6_M3jDeTCByJzh0NbzkdCdPP&amp;camk=nUmJqO2E8rhFV_DH-PKJDQ==&amp;p=6&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D8" t="str">
-        <v>Los Angeles, CA 90067 (Century City area)</v>
+        <v>$80,000 - $90,000 a year</v>
       </c>
       <c r="E8" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F8" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=e46ce81efce8393d&amp;bb=7CMKH5B_VZ3BKSh5duqStHjrQ1XhJs5XR2SaRmn3DzyPXoq5aqvu-ubxsjHK5wNvaTElonqDJ7Ma5QloLk-_Tv0Lk3IRoslPseyK2fQdnE83NF5uNSq6wzljMXLcD0Uq&amp;xkcb=SoCa67M3jDaggQQHYJ0NbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H8" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Principal or Sr. Principal Price/Cost Proposal Analyst - Level 3 or 4 (Clearance Required)</v>
+        <v>Mavensoft Technologies, LLC.</v>
       </c>
       <c r="B9" t="str">
-        <v>Northrop Grumman</v>
+        <v>Program Planning &amp; Scheduling Analyst</v>
       </c>
       <c r="C9" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0AuXXgYAOnYKE4tUBnMU2qW6DTGPYHlsEerB24vNTe8oyTIzRHM6XKYX4J9asL1rga3Iba6bmGN8_MTY8IpYLaBferJiaQ5uozBRj3UtkVJbwjNG_WdkaqeNgtFwmZAapugg-cxdcVBt_qUIwyGP2paa9XSjVqGKAjxffAESWN46qAhho-P4zhREpNTtSOCNgUsZl-AuwT6vZ1d2GO1KCcpji4csoEe37hCZSDy4cjZXjarO5jxhDGqrMgXGjx_xfnN4EoLCO-lFzqmt1xQKwgnvHJPm5NR6QHEa_HNJXIZXXxk2dYv4Ug_WgG7ZfQbwiHyRajhYj_Bwc3rnD4MWz2qeiH6EyRslvp5ID-8-Cc5b0wzBvBJ60V2jNoTR0cWkherKk7ScD1e4PpDwW4PsB-bMjcKaxNlP5yQitqKTIur8bacrEF9M47bqKj1TKhyAU3ctrrtFtk6arb2HP8xBJ_hCH_yUtdeilXItjKLL8OUDw1iqW1qiBgPpkRIemU1Pu_MJN0XXO9xU_gQH7eDVuOsf5jDWBuu748ZmeXXyxNvaiy2fJuYqz6WT7tPOOMfD3PrlGyR73GAzh3YAUuaX4XQ65G_RXv6nhYD4tb4Y0XmJcRWLndG9SuvI9rnfNay2PaZaj6I0Dgr_QTGQYvZNcXUuzKgEa_HWhKePGrgoBs9GTbhVAEoleo5r0tfRYIWkmkKJrKQP_WqKxU26R2dzpTU&amp;xkcb=SoCk6_M3jDeTCByJzh0MbzkdCdPP&amp;camk=4HOcmqOLYrAWX5GRe5XyZA==&amp;p=7&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D9" t="str">
+        <v>$90 - $95 an hour</v>
+      </c>
+      <c r="E9" t="str">
         <v>Palmdale, CA 93550</v>
       </c>
-      <c r="E9" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F9" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=61df578244f0193a&amp;bb=7CMKH5B_VZ3BKSh5duqStLiE74o3RmvsI8lpttCrM-HCFhlUvocvcGqRjxCcaCnYHLN20_Tq7GOAYWTk6HOAAGyidcRHJZkj98QvznNW2lzUOW9RfZBLKG1EhwP4gl9p&amp;xkcb=SoAu67M3jDaggQQHYJ0MbzkdCdPP&amp;fccid=11619ce0d3c2c733&amp;vjs=3</v>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>analytics</v>
+        <v>No</v>
       </c>
       <c r="H9" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Payroll Specialist - AI Trainer</v>
+        <v>Deloitte</v>
       </c>
       <c r="B10" t="str">
-        <v>DataAnnotation</v>
+        <v>Data Science Consultant</v>
       </c>
       <c r="C10" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=65b87289e914b8ad&amp;bb=PiqIfdvixsxOe9O3SS6y8R7LFnGMiE45wQGkKkSL0SqQcBZiBugWX5U3-mcoH6evs_afb8KpdPiMylQimvjYXgVMcCuJuzezxNE2rlp7CfnOx5a680TeXB2GA6fUkUt-&amp;xkcb=SoC567M3jDeSsKSDl50LbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D10" t="str">
-        <v>Remote in Culver City, CA</v>
+        <v>$93,000 - $171,300 a year</v>
       </c>
       <c r="E10" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F10" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CnM4TERr6XuVBW3VTRACvDXDx9S3Pbn6a0SwhkmoLTiIZpxuUfjFtTqxOVUjTOw8FHjRJWXH8M_sn_PprNXw0UMB46H7v9V5DAKl3mXoDsRQ6-PyULpFN7ludrYKe1bL46Pcsi8JKLpWcj6XBHIU4O2rxcEU5NrPu8lb2HU1Q-Tr9QybUE0mwYxqLWUyAANmmoTjA-R8sX0hpLkXL5bzRuu7_OwjEtfQtuKkApz1Zk88r72e932xIRs7LIS8wZNx03G5Ruccu-8DXOx7XJn_E5Q12cGj9TLPI4dThCHnaNKgpbrnEdx4eS6GKOcUQyB4BeLz6SKdHEBcPCDdCjDvJ4ANSEkPOp9m6Ac91qNw5vnY8ihFRYhWo0ZiOVxppfL_spsdRTEQCjrs45fFULKWMV5Ug4y0LtfK7CWgUdSdMrP-R5hm0oHoON7PDUmDyhqvQc4OJXXhkrpZNrnr9UoE0P6q1-D8RCP1X1jnTMybBjxN7v68aVq_m3cA3iiy9fdg8J6YGqSIbA1kWbdCwuMofzRM4pSGpyE-VMcxbMTskS6TS15iYaj9QpvgfPWLQOhowAZp9uNPO_kHbR8MguAlNqclTMzPj7oDej3Eo3dp2tSIWqC9aoNKANYBCi-hTlhyr7klXNM-5UnvnOP0FYZ-m63qxTx9gywUpl0SrUGai79FkD65Vh2vdW_XEIqOCS7Ro1MD5DcfJsW7Pk1Q1rv76QqoSFT8xew5yNPAwzKCgxm2qL_ZZHFv8Mlh5-yGzOble6B8ic-QiVi4nGiRXIKwQyYlwHV7mFGjYHkrUO5a-bSFsrVSqii0NjlPwPuO8Ov7eiFznuOvX3319G20ZWkKV4qQXfRYu7Ys42c41OIO0KBisol84MK2AbB67LvC_yLOmqWVSS-xP0VUjb7opS25D1JtSnXbroYB5XrgFMkkFVGg==&amp;xkcb=SoCJ6_M3jDa_yRQHcp0LbzkdCdPP&amp;camk=UoKtGZLa3XIoupJahZNehQ==&amp;p=0&amp;fvj=0&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H10" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Payroll Specialist - AI Trainer</v>
+        <v>Deloitte</v>
       </c>
       <c r="B11" t="str">
-        <v>DataAnnotation</v>
+        <v>Manager - Bulk Logistics</v>
       </c>
       <c r="C11" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=6b8c6e31bbc43558&amp;bb=PiqIfdvixsxOe9O3SS6y8ahcUDdxllrkKpnpANp-mB7dXExqsWFEb_I6zDFQe8ysc-OxPVU9JTTit2SyhsbcmfNXUZDy2zc_d2lDM9R4cwpUWnzoUB87X9ZwepNYDIZd&amp;xkcb=SoAN67M3jDeSsKSDl50KbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D11" t="str">
-        <v>Remote in Burbank, CA</v>
+        <v>$144,200 - $265,600 a year</v>
       </c>
       <c r="E11" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F11" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CnM4TERr6XuVBW3VTRACvDXDx9S3Pbn6a0SwhkmoLTiIZpxuUfjFtTqxOVUjTOw8FHjRJWXH8M_iUUhINV055GAkEb5_iwu6PF5saLL86MJVCLosjGsOp750lyQ09liQfehyRCuvAfhser13AVxyS0ZJSqK9YhF7it4F1YHElXdsoVZtssJmqyLaWo0SWAXyT4wVGvfTJ2_4t6q5RRMLRk4w-OCEFNWpadlU1a0YDBrlvb-sMeKrkeXG5df0u01XBK1NnzCbX-eOY2RntWIiEosfvevaQmFNdkld2qId2_XNgNUwJv4mYqQwptirHdD7Nhhp2a4lmyIEg2bM-XbXS9OWJy5W2RIuYf_n-I6wWrdNegMHe9hbnAViEAoHHqQv-q66QgtV2j4ysiLmWQHTypPqF2LLEn1zwL0g6kBTJT49CUuvcH7pf_F4YToZJVDuUbO0jrq1SiThOiME9H5LshxN5XC3GliFcuZWYLXEr32Le4kD0i3ogO7kc8XnXj3Ze_e9Sw0ikbZZvs-y2ubc2KSAyYuahtYVhD_Z-hrcJlqEIk9aJUsc7lyDLPyhKv--MDkVQBrD7WyVAGhRCu1VkAXaCEDsvIOWOFy01lZcXJsRebYepPtX7rUz8wIHn8qJugD26OgQSVXX7EXWtU7pu1KtWYmS96BryJ1K8eReNzaWMZvkBqIZduAJ1waL-3Jk9BTp_6v5c4uAtCE26bz3VR5U2bKArXuCRZ783G8r_GPjyCpoPcoNfSCEcD6K5yKOZHTdsY16jYHL8oZIFDEQerHA3ZMWSdJmlswgm1bKNsXoIsWPqJHKiyM7Tg7dEIMXqtu49Dgkwe3_ZRWgT0-GtWWMaz16zfhBW_X4CYWVFHQbFj41DwiiVh2bxLH8z-tf74P2sTaDeTdrJWoAWomfv2fHrh9p24ECM=&amp;xkcb=SoA96_M3jDa_yRQHcp0KbzkdCdPP&amp;camk=UoKtGZLa3XIoupJahZNehQ==&amp;p=1&amp;fvj=0&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
       </c>
       <c r="G11" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H11" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Payroll Specialist - AI Trainer</v>
+        <v>Accenture</v>
       </c>
       <c r="B12" t="str">
-        <v>DataAnnotation</v>
+        <v>Knowledge Engineer / Semantic Expert for AI</v>
       </c>
       <c r="C12" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=f6333c7353884a33&amp;bb=PiqIfdvixsxOe9O3SS6y8aBZqHK8N5uyO_kA8k3TUmM8-bYNxme2yZR4GoApiDyHllkrufepdPgv5wnFJk9g9TvrKU1K6U9VxQKUzcBzFv5Bl3RWx8pvR9q3yXkdXR4p&amp;xkcb=SoCQ67M3jDeSsKSDl50JbzkdCdPP&amp;fccid=a4e4e2eaf26690c9&amp;vjs=3</v>
       </c>
       <c r="D12" t="str">
-        <v>Remote in Santa Fe Springs, CA</v>
+        <v>$68,300 - $220,400 a year</v>
       </c>
       <c r="E12" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F12" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CnM4TERr6XuVBW3VTRACvDXDx9S3Pbn6a0SwhkmoLTiIZpxuUfjFtTqxOVUjTOw8FHjRJWXH8M_kAW7AL9sJolcgLD_TjorLghwMWITppus1QlFNZGjSL5g7JWOlN_SNMUTsPTpBuudw-HSUUOkhjX51cBzZO72CSiOe-ylsa9GW3kk1kcA_eKnKxUM50zN1TcxvX0ktl1DAMnFFQ_n-IdrUP2fqIwJV9h-QSJgY49dAI-vDEt-3yL3rOevBm2ycawKvqHJXuAlmo4k8uslCO1_nTuLdbkYjNIFYgiHmfvAoF7o21GM1Xxo19KNQj8YQgbeTBn6y2y1__2NBoZL6l3h1oJI1aZm9mw_qo-V330EmdafndfzeGy_TWRuj_xQEtaC7euUeQc3tLreOdVCIIgUVXiP6f4M2XBU-quYreJejZL2Ogb5fgSGkCkqHNyxuSlZlSFaub3RbCmsVQdGDZfBYRY-NDtmbpAjtP4qB6w7RWz3uVYTbVLUeWwMnQ2obhvojmH3NTnXsyysR-xaRqZMKkDg-aBwu1EpH63AIvc0TKoESBBTN_cTGFrE5E3_1iM-RGQC3Gj_acynWiOXFzyv0IhckwMCK4BFT1FyrwOHTRF06auIhvFJVqtJFv2ho07B-Ua97n5Hb8bYLMo48DamzfEg2Dp1yXwRSD84g3jb42hDmUepilzVdq3qdC9OcKNAc8LJP-nGjfaK-LIQ00ccwz81CbOVwp2Qshl-Z1K7LFcwSAN5_yO321Bl6vfhTpRJv7dGtPBiV3J1NQhUb7ps2XhBOE45AJqgc7STp7cGlgbpGucDT8wFk8R7mpymtKV7juJn0zJ7msB2dsbvRtjh7AxDhs0Jp9wXL7x16KV62YUTCWka1U-sKLj45Y8xd2DseDKsqAHB2vX_fOMI65Y_MaeJq19KHsP9A8uvXT9Gg==&amp;xkcb=SoCg6_M3jDa_yRQHcp0JbzkdCdPP&amp;camk=UoKtGZLa3XIoupJahZNehQ==&amp;p=2&amp;fvj=0&amp;vjs=3</v>
+        <v>Hybrid work in Culver City, CA 90230</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H12" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Payroll Specialist - AI Trainer</v>
+        <v>Accenture</v>
       </c>
       <c r="B13" t="str">
-        <v>DataAnnotation</v>
+        <v>MDM Architect</v>
       </c>
       <c r="C13" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=7b89f671bb813ac0&amp;bb=PiqIfdvixsxOe9O3SS6y8VR7YzAbRyca56OZRMtyp8x2NX3yANkk-9U7s8ipZTiu5fC2psj9_au8t-Nu6KGsQar8ZCImXY9dBtZcD-gA03MG8ZNbQtjja4Ur1yoH2j5Q&amp;xkcb=SoAk67M3jDeSsKSDl50IbzkdCdPP&amp;fccid=a4e4e2eaf26690c9&amp;vjs=3</v>
       </c>
       <c r="D13" t="str">
-        <v>Remote in Van Nuys, CA</v>
+        <v>$87,400 - $293,800 a year</v>
       </c>
       <c r="E13" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F13" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CnM4TERr6XuVBW3VTRACvDXDx9S3Pbn6a0SwhkmoLTiIZpxuUfjFtTqxOVUjTOw8FHjRJWXH8M_tvDs7SBIPLEkq9O9FvjYPhrXg_YnBMoWbaQWWnwyuQl6gp3ZxxJ51heM0U-3ZM6QROUaFfDwbc-cZZm0sJ-VDX4BUnMpROZtRHxwCu63Iv2pjhMmyfsAQuRSSziF-6nyTOZswfiVrLQkMk_AsB9lVPQ7uHpx2c8vHFM9U5atEAG-IvSXPxuvbwGbvw_vpX0V-osL9E4RInX_yyMSyj0Lwi9zLiR3DBwUdZsCVA1eECUiBGJsWyZvvYIlGL3jM_zN1yQKJeUo9VW0C8vRft_gin1pGdUHaVEdQUUA88BSCcejxbBd_KMh7zq81hB846GJrin4Cz0tMhBI1Mxjsawi6ItG-m8zLV4x6QDrlAB8W5iFILNb-Ff0TlQGstnrsi42EWPvzWMaOuqfitUVN5sA0mtmcxqHkeUd5Ki3BZkjh4h1y0XewTeD87aKZMV9NjiNRDrnK8GTEE0UQt0ZwM1YcGdS_oGDLqxxW74T9KCA3DitIq7VPdLVSHjuhN_dVn6BGUnBb7YmZbbbMBHAyD1Q-AD70IhnPGwKbANlt0OelVKtoGVqRyaISLWQUSkr_Zu7boFVIkLvR40UBKHTXRWdvJrjit9L9t1g4qwetKwnWzNypBjavCfO7mdcSLsRjtoSD4_LNKpd3JI9wuc50C7mpUQ7_7ObqY1w5o0kF7qwnhq-u3tdql5vbGjnrPhHeSaU92IdVWA0j7ntumLAGiJzvTx-04ZEIGcZmyc_U52deuIEKApQ6NGOmF_mvn7URLST51dflK30A5Hh0TkHvyK9Nwb4AobPqH_-DXnDZn3qRgQz7qivz_6QQaYcDRCR7Ho3Ir5NW8pkD3mDxTNtjy-L54=&amp;xkcb=SoAU6_M3jDa_yRQHcp0IbzkdCdPP&amp;camk=UoKtGZLa3XIoupJahZNehQ==&amp;p=3&amp;fvj=0&amp;vjs=3</v>
+        <v>Hybrid work in Culver City, CA 90230</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
       </c>
       <c r="G13" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H13" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Senior Data Engineer</v>
+        <v>KPMG</v>
       </c>
       <c r="B14" t="str">
-        <v>CyberCoders</v>
+        <v>Manager, SAP Technical Innovation - SAP Business AI</v>
       </c>
       <c r="C14" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=80520d8db7a22e40&amp;bb=PiqIfdvixsxOe9O3SS6y8d3XfyjOq20LKeJ2rbsuSdZSJtb6Opt46LF1s-LGpOD2bly-0R_uwETVainlzK0563ZizvUYAv25-uhmJJzOG2hpkAwA7w9J_HXVJyd9bKWz&amp;xkcb=SoCq67M3jDeSsKSDl50PbzkdCdPP&amp;fccid=2dd390c3a48a7ed0&amp;vjs=3</v>
       </c>
       <c r="D14" t="str">
-        <v>Hybrid work in Los Angeles, CA 90024</v>
+        <v>$145,350 - $253,230 a year</v>
       </c>
       <c r="E14" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F14" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CpFJQzrgRR8WqXWK1qKKEqALWJw739KlKqr2H-MSI4ekNwaLJNGpJ8ArhG7wwRF5agnXKQSas_vTWmdD8IvQ9FRjj_L2wZMgPwZ_EkSwPNZxfsWGqne21yaxXtoYcUUn85yGeuJl6jloeTub5N04PEJic9OVEqK6pl05V1NNMOmYZ8yetk6xO62Dhvs8CsapwefV3NS-xTEHiUj4q73qC4jeNHTfzDev-y2rdwp5S3DGZLhzjzo7lOrWUg-IHi4Sufp-GKIjI3sIUsD89NcYiwJA5mFMPrHrkg8xifTszwYzQcaBaF-LBN_w0-xSeatZ37XkG_PJIEkY7mOIrIhQhCrwp2Kz1k5IgjGD88kDsZFDMNZE5peWkOHdRdjfqtqmC-opSqoUmoiJAe6hkiSPZpztbu1N1FtzYhtk83D60hpRmcLYDTq_hGzTd0O8rseugtFtwDNrEr3GiDZNOLWUmpzGU1_oNE-A47zRNiMzrTkUvPBrxiFxW06q4xSJQeyMI4BABTDt1dRbo7e9vUxoWMsASpxijt7dJbjLHYZQ9rc13kf3EMhTArrJcu35nf8A2lZUICha3iuyAQKdcwhZkDFhD-8Mk7-Y-30fuzqF_xG-EdsRhBOVtqDuwa2x4XAYrqlO5rQNUDCTEBGmANjl0bxzIfnq5XoqHoSrMHR-vkfsI2jgEA46Auao7sB3Ldg4KzTrqEGOBf-ZaSCvNpkA72JgxLKtPSC0oaRMRAyoSrUH7ufGTXe3hqY2Jo0djI7Ney4McEc9qvDqTr2UAiPLBoikO-NF8R6rLMiQEOq1RML5mISWb5m75gvcfWHum-dXsDv1Fgv--vYW5BO-r7E0hGX1SHQU6iHAzTvq4tmpi8EzGXoZa2r4ASjPZY2E7UMJmzs6Fk3AH1jNcGnRJPeynT0rD9pCXwO7ZQdcsYPKfmKpw2z0Q32cz7UMmzoBuYxdDlpX-bShkIYrwXdqPewUvppI2Ty7F8E4s8NudEdhIPv-DwjkH-S8L-Hiiy0ZIujNjzWGeRRXyC1Xp_XQArSw3Ya3smE1ZU7IQ9aLH10LDfwqNcg0eRa_5H0QtEvjhLmM4s7yqOWfThrhZayev3ucdtSEEgJUrIQKqjP-DPRvu3VZr05LqVYAPr0AGeJ2XwQxdt4xm-c7Z4O3GrFlKwxJo_dwCcT90VEN5YM8LoUYvADTwz5jQJ8OrKo8gYbH5kPfGc_jcfHpNEZ_GXLs1DlBSxVk5vlKSPWjxZlS_aTpdH6cZKSGHa51VdhhlY1DWqFkFRRJvCkUmNwA==&amp;xkcb=SoCa6_M3jDa_yRQHcp0PbzkdCdPP&amp;camk=C3EPSzFlQw9q7qx2RKIvRw==&amp;p=4&amp;fvj=0&amp;vjs=3</v>
+        <v>Los Angeles, CA 90071 (Downtown area)</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H14" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Smart Thermostat Engineer — C++ / HVAC Controls / Algorithms</v>
+        <v>Omni Solutions Services</v>
       </c>
       <c r="B15" t="str">
-        <v>Nuve Controls LLC</v>
+        <v>AI Algorithm Engineer</v>
       </c>
       <c r="C15" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CPON9xshdASMo_1n83A0f28SzFzuwG-28bCOdvOyb56i1lhRUcE9wvHETk05cPnfH-lDblyo3cR3_Sc7l2FGrCHvKLSvUKSshzBI49V61FpzCsqvvCV0XR0p5SLufKVe8DRjDlRWGEN7s2un8Ndn0EES_ABjqF33tQ42mitxxPRRr1q-oGx1kLmwFmdZBXKU1rvwOfnHbAiON3GVUQ954OeVZ68uSmgzcVGl_yP4QwR6cqTLr3NtFcCdaIgJ8ppDCesJ0WesVwA_OPJx8Nnf8BTQ71IhiyZb7DH278CirY_ObQqqRnWL1HKYXWYsoNh-d-5Tx-8vYjuqsLq3S4FomiFvU3Y-_C6OqocqJE_Pu8dbc2KCQjUKc4xWdlaLrNsaZdQw0y29PfnuD7rpjW43eEGNX3OXxxorNw7mQmRI6bB7jlKJgNmr1Qmqr5-HBt4PcwpMdZs544ijgQiSZb2X-4VXxumTvnhkY7Lr-P-WQCGEGojFH9kRQmU-EZSo2HEx6uMkXNoqde6FrdHmRPITBPowe3swlDAU0uptPMhd0GsF_F-Up7bPhv_74phTSZr9gTbMxMqD6gi3aONLWpNaanRSY3xa2VecSDdv5s0PDwOkCGqq5YQr8V4y_6XSSbPyRZQu0kfJRljAmh3MSm2_5PeFR0hsNji38Olazn_rWSxvmSIygXRVnaaaAekV911iEEIyYvMZyaiiH4w5yOyXMY&amp;xkcb=SoDq6_M3jDeSsKSDl50ObzkdCdPP&amp;camk=C3EPSzFlQw_DVLSlla_-6w==&amp;p=5&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D15" t="str">
-        <v>Hybrid work in Tustin, CA 92782</v>
+        <v>$80,000 - $150,000 a year</v>
       </c>
       <c r="E15" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F15" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0ALKPWsQgzrKS5DdNKPAB0KiFHKLm6VsNmP1tr2g-zOHMYUoNz8r__j-tWB6tlYeWK2plxocwuI7NX_HeLTGziuOEYEbjFvFO7XFmPdc2DySEVrnpOTE-zOb1WoH7lftmuTH48S5isRI2Znbh0GA7tY2nfebs7jepbdkg6DAXTCkTVPeMz04XoMZGo62j465ueRBpphaXgzMjmK41SyoCbIn9IHvMujtLwgA-dR_ZJPyC_-PcSLkYHp5bgj8hTVlrwU-umzjCZSOSGF-TMLdwAGn7MVKU5REFFzdvj_409u5TihjzmzSAeTSmeev8A-6OGSOvWhodyEt6A0Oh6Ny0ojm-xQ4ZSG3Kq-8GBq_zr049J52TyL-BmzUa02-fnpHh-CUDMvHVYAVqnzGkFAL7LykvHH4AFR1JfmSlfHn8W6-73MKdk0Y4usMVFmLMl6YWtQrmk6d-Cot9TES7-HRiuVg-eCDCPEfAZwmzEXWGWhHyVMr6r-F3t9j6Qs8DtD2P7Y40PRsjoMBxxmDPGeeEs5QZ_F9ZWcqa10d7X38ybDWuCYcZfhzY1eA7kvDnA2m700ILTJ1VV8fbPjicizwmWN5K7_E_EH2G8592w9OhXrmtzUvlwmRXV_8peSyF_dRBs4ggCZ4ZfT_73zwiXTMx3w9epgkwPZZbmd8e78i5zJ55WXE3WXF8teZtogR2F8LZRWuqO0i-aH4JESkfft03PbkUjyx4tkrihZBdoC3eP7gSwTE-4VIveI1kYlCXnqmfE=&amp;xkcb=SoAu6_M3jDa_yRQHcp0ObzkdCdPP&amp;camk=C3EPSzFlQw__kXJp4Q0SxQ==&amp;p=5&amp;fvj=0&amp;vjs=3</v>
+        <v>Hybrid work in Arcadia, CA 91007</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
       </c>
       <c r="G15" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H15" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Senior Full Stack Developer</v>
+        <v>Deloitte</v>
       </c>
       <c r="B16" t="str">
-        <v>Motion Picture Industry Pension &amp; Health Plans</v>
+        <v>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</v>
       </c>
       <c r="C16" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=0a6e81432a843a50&amp;bb=PiqIfdvixsxOe9O3SS6y8dCQmC4GuN8ec5yks4wyvCPX1TafNWcN7e4VzR_JovJNlQSWxM47LEkX-Non16FvHKxtDvqxlV187WYSdLHJ8ljRhFCs5zKs-BqaEdmCZbeL&amp;xkcb=SoCD67M3jDeSsKSDl50NbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D16" t="str">
-        <v>Hybrid work in Los Angeles, CA</v>
+        <v>$84,400 - $155,400 a year</v>
       </c>
       <c r="E16" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F16" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0Df2ZXQkQrVei7QMlJKqQnhPMfkXmZ2JHFrtIKPrV0FiquWsAcnFNwuvWC7nbkSY9PLqWE-SYcyB5JdFDSYc4MniAMyDcfLmOy_iEapfQC-EdUMn1lQ5rd4mBMDo4g_DTN3Sh04Jxwacez1w7lgDUlbJ4tG0KKfrxX879fxHYG0QZsaIwomdUylLsyKG1AUQAk5aWdX8tQdsuKcls1KD50GKKSeWgLFmKRDCb_b9FMD_LykiV7ttpU9fBEd_ag9Tm5WjFgFWeIorPbVgedEsYIAHyVJPKcCT0sEiLo0HQWpzt5n61E1f_3ZPqcXR74XkUDU9CfeOb12wFOofMUlGE6TWdiQ_TTBPW0R_KwMQGX45rzaWYJewfDFyuqlhhLK2kS7Q4BWNiZo9sejGE88EWRNwMOiLVo5XCZ4wp9BlemNXwHZcJwy4-yep7Iw2gBDqbls5ctQdEbyN2QtrP5ip7ah49H-6TsLO4u0wfBOtec5jn1MI7ouTKa0WM6k9wQzgxmJqWFdK5znAGHg8COQuojKBUmnKuF6fIAkUD7T_Ldgr9bpDaPsFVB2XsSpWPPFpCn8mhp5rJR2xxsb8kCVZNUwgqqvCLdW9mz7BnAMm0RSQj5mCAXVOzsAjfLb3tJN5AaM8HFaXbIkjcolclZyaFCanuN3xH0sv0qo8TptUs_Ulv9YE9qctZvgBztc8K57LMi_Nk7KwURCuw==&amp;xkcb=SoCz6_M3jDa_yRQHcp0NbzkdCdPP&amp;camk=UoKtGZLa3XLYYlMGlXSz5g==&amp;p=6&amp;fvj=0&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
       </c>
       <c r="G16" t="str">
-        <v>artificial intelligence</v>
+        <v>No</v>
       </c>
       <c r="H16" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AI Engineer / Data Scientist, AI Sr. Manager</v>
+        <v>City of Hope</v>
       </c>
       <c r="B17" t="str">
-        <v>PRICE WATERHOUSE COOPERS</v>
+        <v>Staff Scientist - Computational Data Sciences Shared Resource</v>
       </c>
       <c r="C17" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=164454b8b33585ef&amp;bb=mcS_s2h-jFOmthw8YRlzLvCKVPTWuSIlrgOecwMksBAeAzaWQ5dOoQB9DdAPkInGHwMp3pvgTi9Fhp1WwGuaX7d4KhNCbOcx-8m2AviXGyoRrtxIzwf8vzdRjevVJRqB&amp;xkcb=SoCF67M3jDeunOwEE50LbzkdCdPP&amp;fccid=e4c4ad85ebf29819&amp;vjs=3</v>
       </c>
       <c r="D17" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$38.96 - $132.16 an hour</v>
       </c>
       <c r="E17" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F17" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=3b5c86861493d0b3&amp;bb=l7BJmXrwFkd-zVQyEv0ULOyxBI2B4imE5CQNJFRfQE8PjO6qxthvUcLnY9B5JY9E_ayBjUT4nnTslxOEuH8LVcguKiVuSpF5rQBIDpfXvUmoLJRORCQGDpSHesTgwo2Y&amp;xkcb=SoAP67M3jDa_dewHZ50LbzkdCdPP&amp;fccid=5e964c4afc56b180&amp;vjs=3</v>
+        <v>Duarte, CA 91009</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
       </c>
       <c r="G17" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H17" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Data Scientist, Apple Services Digital Marketing</v>
+        <v>PRICE WATERHOUSE COOPERS</v>
       </c>
       <c r="B18" t="str">
-        <v>Apple</v>
+        <v>AI Engineer / Data Scientist, AI Sr. Manager</v>
       </c>
       <c r="C18" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=3b5c86861493d0b3&amp;bb=mcS_s2h-jFOmthw8YRlzLrOIqYUNGGb3wgT1NrGQhT83-Asq-OirLfl--kRrP9kWOoAN7tqzcFeslLZ9BLugZhvIezz3W3yNKs3QSpfijRUR7-ILWoXFVpBLO3bai94g&amp;xkcb=SoAx67M3jDeunOwEE50KbzkdCdPP&amp;fccid=5e964c4afc56b180&amp;vjs=3</v>
       </c>
       <c r="D18" t="str">
-        <v>Culver City, CA</v>
+        <v>$119,000 - $337,000 a year</v>
       </c>
       <c r="E18" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F18" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=b8dd6771dfa382b8&amp;bb=l7BJmXrwFkd-zVQyEv0ULDAHbX6f0jO0EZcjJdGZbkRPPW7CPyCJbDn0KG7R6XwO9GpmCVrfkgcxVbVR5uYOS0wsGIKs8Rnys7YwDkpwRywCGIMLnK3ZWSAv5HVcT59q&amp;xkcb=SoC767M3jDa_dewHZ50KbzkdCdPP&amp;fccid=c1099851e9794854&amp;vjs=3</v>
+        <v>Los Angeles, CA</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
       </c>
       <c r="G18" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H18" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sr. Validation Data Scientist</v>
+        <v>Apple</v>
       </c>
       <c r="B19" t="str">
-        <v>Rivian</v>
+        <v>Data Scientist, Apple Services Digital Marketing</v>
       </c>
       <c r="C19" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=b8dd6771dfa382b8&amp;bb=mcS_s2h-jFOmthw8YRlzLlJ-3VjwE8Ocio4fUx7C-bgpZj_1Kx5K70bIhxgvqO8unTNeUaqL_txHJYNj08ufnireEM1xVZCOca6UKi24UUqjMCsAr-lZzQ50mnONK7bi&amp;xkcb=SoCs67M3jDeunOwEE50JbzkdCdPP&amp;fccid=c1099851e9794854&amp;vjs=3</v>
       </c>
       <c r="D19" t="str">
-        <v>Irvine, CA 92606</v>
+        <v>$141,800 - $213,700 a year</v>
       </c>
       <c r="E19" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F19" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=ab81b58ee6134007&amp;bb=l7BJmXrwFkd-zVQyEv0ULOIWbNYBBSTbeQOdgKd1qD0jCwUs-K9suGbAO5l2iAcwxfpMsxJdUj96ZzWR0g62n5RuX4Uow4idhwZi7AjS4S1QepLrlXzbrr85QgSTya7L&amp;xkcb=SoAm67M3jDa_dewHZ50JbzkdCdPP&amp;fccid=ab392afaee93f976&amp;vjs=3</v>
+        <v>Culver City, CA</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H19" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Knowledge Engineer / Semantic Expert for AI</v>
+        <v>KBR</v>
       </c>
       <c r="B20" t="str">
-        <v>Accenture</v>
+        <v>Junior Gen AI Developer</v>
       </c>
       <c r="C20" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=84745e9e02a58677&amp;bb=mcS_s2h-jFOmthw8YRlzLjhIB4EZhpQRuXZnHqA3D5pT4cMzIc7AWeuSbF9ymT9AGxLDlyuaVDPjagMdFbuKns36bUpnQaKhE5ph4uOLIoUl5a-f4omHMNiMutOFo7lR&amp;xkcb=SoBW67M3jDeunOwEE50CbzkdCdPP&amp;fccid=cbfa56f19cc95796&amp;vjs=3</v>
       </c>
       <c r="D20" t="str">
-        <v>Hybrid work in Culver City, CA 90230</v>
+        <v>$83,000 - $90,000 a year</v>
       </c>
       <c r="E20" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F20" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=f6333c7353884a33&amp;bb=l7BJmXrwFkd-zVQyEv0ULCLTX0US0sjoOW74RHMFj3dNpwc8mMx409tTa9R9k8joPl68-GcWBQcULmISR5a4A76CqjH2gwp3KJiLWjIldVWKE-oGhY0Th6CDAAPvr8i4&amp;xkcb=SoAc67M3jDa_dewHZ50PbzkdCdPP&amp;fccid=a4e4e2eaf26690c9&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
       </c>
       <c r="G20" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H20" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Junior Gen AI Developer</v>
+        <v>Bank of America</v>
       </c>
       <c r="B21" t="str">
-        <v>KBR</v>
+        <v>Registered Private Wealth Client Associate</v>
       </c>
       <c r="C21" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=61ce508a904e0e02&amp;bb=xTtqbixbr3tOCzQpASvx9xwOzfy8fH7N4Vg0prY_ObZ7Q4bajhLcRLaXYE3smDZVroa3POHNsUd7j0_rxzIFKYl6-bWBNdzJoNLFZlxd5sO4v6F7tW4m7worMQGETiNx&amp;xkcb=SoB167M3jDerBcSgHp0LbzkdCdPP&amp;fccid=5bd99dfa21c8a490&amp;vjs=3</v>
       </c>
       <c r="D21" t="str">
-        <v>El Segundo, CA 90245</v>
+        <v>$25 - $44 an hour</v>
       </c>
       <c r="E21" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F21" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=84745e9e02a58677&amp;bb=l7BJmXrwFkd-zVQyEv0ULC3O0p_Jqzc3lZotAcod9bXt5ZK30QC0st-RHhR9uC_ohfgtsQT5txXIbQ-wPn0gbD_m-uz-Dj_yvGmtovfPmjKSJrrcmnMveF3vy-dOw0mb&amp;xkcb=SoBo67M3jDa_dewHZ50DbzkdCdPP&amp;fccid=cbfa56f19cc95796&amp;vjs=3</v>
+        <v>Los Angeles, CA 90067 (Century City area)</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
       </c>
       <c r="G21" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H21" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Analytics Engineer, Sentry</v>
+        <v>USC</v>
       </c>
       <c r="B22" t="str">
-        <v>Anduril Industries</v>
+        <v>Credit Union Risk Management Analyst</v>
       </c>
       <c r="C22" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=a8b6f884dbf6036b&amp;bb=xTtqbixbr3tOCzQpASvx99SwKxmRxxzR9ROF5H6niI7hzFXB168-ebKq7Ris09RUODzxvB8I1t_Ca4b-8OdagfXewRGps2zsTMXMlD2TVr4G6Xbrv40vEH1fmMMJ1rJ-&amp;xkcb=SoDB67M3jDerBcSgHp0KbzkdCdPP&amp;fccid=7455773bace145da&amp;vjs=3</v>
       </c>
       <c r="D22" t="str">
-        <v>Irvine, CA</v>
+        <v>$24.50 - $29.00 an hour</v>
       </c>
       <c r="E22" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F22" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=29b2f5c81d3ba672&amp;bb=l7BJmXrwFkd-zVQyEv0ULExEUvyCIP-sOuAtSlAR_71MdN8sIDnteQbNjpp963XoK-dLJtloOHap6WmOakO421FA4ryEPnKOtvU5KymEq1S2q4MqwD396LnZyZDzy5ay&amp;xkcb=SoDc67M3jDa_dewHZ50CbzkdCdPP&amp;fccid=3f7b0eacc8de6549&amp;vjs=3</v>
+        <v>Los Angeles, CA</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
       </c>
       <c r="G22" t="str">
-        <v>data scientist</v>
+        <v>No</v>
       </c>
       <c r="H22" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Chase Auto Strategic Accounts Director</v>
+        <v>SAIC</v>
       </c>
       <c r="B23" t="str">
-        <v>JPMorganChase</v>
+        <v>Launch Cost Estimator Analyst</v>
       </c>
       <c r="C23" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=7658cf6155f6535a&amp;bb=xTtqbixbr3tOCzQpASvx976dQLDh6Tbi_ZnfFVayeTMoPeKIk81h9Nr-_kQ7FoKAfbPIoc9Npvc6lH4q6aEKW5PEnbPSyILhTmRVSrrs9kLJBm4voGmtbH88w13xR_ge&amp;xkcb=SoBc67M3jDerBcSgHp0JbzkdCdPP&amp;fccid=f3b836e645f9b36d&amp;vjs=3</v>
       </c>
       <c r="D23" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$160,001 - $200,000 a year</v>
       </c>
       <c r="E23" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F23" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=40dc863d5808015f&amp;bb=j7EEicqles3_Ax4IwwLsZkysALgKpoEm6MPmjnfEr_d0Zw59kvRzQtoucv8KAnD9dkZy-HzXLb8o0Jj2BIrG2Xcxa2oh1jum_hkr0KJ3TBn2gHY_GlzVg5ZB89tH0FvN&amp;xkcb=SoDk67M3jDa-65QEE50LbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>El Segundo, CA</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
       </c>
       <c r="G23" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H23" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Senior Private Client Banker - Financial Center - Ventura &amp; Libbit - Encino, CA</v>
+        <v>The Walt Disney Company (Corporate)</v>
       </c>
       <c r="B24" t="str">
-        <v>JPMorganChase</v>
+        <v>Senior Financial Analyst</v>
       </c>
       <c r="C24" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=1a8bbc1e101aca3d&amp;bb=xTtqbixbr3tOCzQpASvx96YMeITvG4uZU4jU3ob65hGNRvNDvCl_9wEseGffF2g5ODgqahpAJTuORSx7GfNFL8CBBN3nT2-23w8_MZgkIiBjUhpvPqOFIp5yVTpTh1xc&amp;xkcb=SoDo67M3jDerBcSgHp0IbzkdCdPP&amp;fccid=4ed80f3a97849f22&amp;vjs=3</v>
       </c>
       <c r="D24" t="str">
-        <v>Encino, CA 91436</v>
+        <v>$104,800 - $128,000 a year</v>
       </c>
       <c r="E24" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F24" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=fa2b29f0b69053b4&amp;bb=j7EEicqles3_Ax4IwwLsZm3HZx781Vjt12HmZqUcjayrokHKPWtujocJuNPlHTfsr-mHS8DGpWjL4JLvW16CC_3CHUSXEMl42JUFVb79urjWznOCpPBouzG9csRkkSAs&amp;xkcb=SoBQ67M3jDa-65QEE50KbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>Burbank, CA</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H24" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Relationship Banker - Main &amp; Raymond - Los Angeles, CA</v>
+        <v>Amwins</v>
       </c>
       <c r="B25" t="str">
-        <v>JPMorganChase</v>
+        <v>Associate Underwriter - Commercial Lines</v>
       </c>
       <c r="C25" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=512cb8742188fcc6&amp;bb=xTtqbixbr3tOCzQpASvx9wUn6wD6II3IfsiBWw9ZR3tmGdnwbOGVsYyYeijLiZhwCgPOZC_kaX3acSeHQFTQBF0wTYfQXQBKkU80DC3UMzvN6Rt_BcY4liil3yOu24Rx&amp;xkcb=SoBm67M3jDerBcSgHp0PbzkdCdPP&amp;fccid=d5805e0a253cf8bc&amp;vjs=3</v>
       </c>
       <c r="D25" t="str">
-        <v>Alhambra, CA 91801</v>
+        <v>$70,304 a year</v>
       </c>
       <c r="E25" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F25" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=c36c32fccccc04ab&amp;bb=j7EEicqles3_Ax4IwwLsZrYJj1p-3lHTWgZXOwO183d31jcV0dtAa0mTHqJX2_ikw5D6X1bYAeDgopnnn63ADPHV5_eN6MWTkCYQsFuQOEmoOzZHmyDZhJwyw2nZvXCy&amp;xkcb=SoDN67M3jDa-65QEE50JbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>El Segundo, CA</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
       </c>
       <c r="G25" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H25" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Commercial Banker - Emerging Middle Market Banking - Vice President</v>
+        <v>Deloitte</v>
       </c>
       <c r="B26" t="str">
-        <v>JPMorganChase</v>
+        <v>Mergers &amp; Acquisitions Product Technology Diligence Architect Manager</v>
       </c>
       <c r="C26" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=d82015e6ecc12ae4&amp;bb=xTtqbixbr3tOCzQpASvx9wqrSD7J-q_6uciqpOereg4j8Le3f5wy1cXsvO03giGEwgx6G6wVuH57W-5Z_OltK2kme1CjOD0OltChf4xuzJAqjIzEBeuk6xl78yKp57M6&amp;xkcb=SoAS67M3jDerBcSgHp0DbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D26" t="str">
-        <v>Los Angeles, CA 90071 (Downtown area)</v>
+        <v>$159,400 - $265,600 a year</v>
       </c>
       <c r="E26" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F26" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=2256bd8b889127fa&amp;bb=j7EEicqles3_Ax4IwwLsZm_e9Of_ffUGFzcncG8Adw6wSmtbnsLUp77Q2BolZyIxUgrjQYdfxBqX2GOeLmuCpaSxccKcVmBgaheCgBtZS8VqUfmcO35BbIKi1wHsgOmm&amp;xkcb=SoB567M3jDa-65QEE50IbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
       </c>
       <c r="G26" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H26" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>U.S. Private Bank - Investment Specialist - Vice President</v>
+        <v>PRICE WATERHOUSE COOPERS</v>
       </c>
       <c r="B27" t="str">
-        <v>JPMorganChase</v>
+        <v>Health Actuary Consultant- Senior Associate</v>
       </c>
       <c r="C27" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=704ec5d5beda401c&amp;bb=xTtqbixbr3tOCzQpASvx9xQnZQMTVvVK8OyjjaeV-SBYU-iPDnn6SqyrauaxqwH2U-ZLNTMhWD5aG7qLa0voyWg1pRP9YwcbTIAsgmSK-RIFfpnPNCll8G-1rw4QJDEU&amp;xkcb=SoCm67M3jDerBcSgHp0CbzkdCdPP&amp;fccid=5e964c4afc56b180&amp;vjs=3</v>
       </c>
       <c r="D27" t="str">
-        <v>Los Angeles, CA 90067 (Century City area)</v>
+        <v>$77,000 - $202,000 a year</v>
       </c>
       <c r="E27" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F27" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=4f5ab94560a11d6b&amp;bb=j7EEicqles3_Ax4IwwLsZvKM5Z_PaUYKP7VUqwUj-u103VLd0mU_d1BHHrzMk3wRj26E6-Z-5JVhvXTL-EPEb6YOG-wha2HjZuaF9FEvHQnI7PZ2ld8QG2sdd_poY3Ha&amp;xkcb=SoD367M3jDa-65QEE50PbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
+        <v>Hybrid work in Los Angeles, CA</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
       </c>
       <c r="G27" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H27" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Mergers &amp; Acquisitions Product Technology Diligence Architect Manager</v>
+        <v>JPMorganChase</v>
       </c>
       <c r="B28" t="str">
-        <v>Deloitte</v>
+        <v>Chase Auto Strategic Accounts Director</v>
       </c>
       <c r="C28" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=40dc863d5808015f&amp;bb=xTtqbixbr3tOCzQpASvx94v_Wurb8FmwnwtmSmjENp2AiamQHpmzXSJINU9giRwO7hYxo8zzu-z_5-u5P-a5rJdQKN2oza9AVeUFhVZrJs2cn2mGviLqOFk2i3eZA-SA&amp;xkcb=SoC167M3jDerBcSgHp0GbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
       </c>
       <c r="D28" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
+        <v>$171,000 - $262,100 a year</v>
       </c>
       <c r="E28" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F28" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=d82015e6ecc12ae4&amp;bb=j7EEicqles3_Ax4IwwLsZjZko0rKQYJoUG8AN5jHyg3dbxR9u1lAbbmXXTYNk0b5-uPbcVeEQVUk2iBsNvvyGpVBwrFiAWq4MSQZo8WK7CwpbWbD9ao7a3C2OuEP8OOO&amp;xkcb=SoCD67M3jDa-65QEE50DbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Los Angeles, CA</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
       </c>
       <c r="G28" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H28" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Health Actuary Consultant- Senior Associate</v>
+        <v>ROARK</v>
       </c>
       <c r="B29" t="str">
-        <v>PRICE WATERHOUSE COOPERS</v>
+        <v>Senior/Financial Analyst | Local only | Budgeting | Cash Projections</v>
       </c>
       <c r="C29" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=502c5ab7201f37e8&amp;bb=zgrb7n3lgNClGEgEYbCx_cMEK7ZcJ6KqkNf6epgBFZrmKcPKvRTQNH0JEAm8JYFuHsbyzEBxKRTw171kbSE14KRR7SedcI59XA_DLVNtOiDdrrt-YVymy52sAOauFX_Gu2lKF8xpG9e0T6ygDI72K29qZNLAi1sl&amp;xkcb=SoAE67M3jDenUNwHcp0LbzkdCdPP&amp;fccid=ee5f7648851a3799&amp;vjs=3</v>
       </c>
       <c r="D29" t="str">
-        <v>Hybrid work in Los Angeles, CA</v>
+        <v>N/A</v>
       </c>
       <c r="E29" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F29" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=704ec5d5beda401c&amp;bb=j7EEicqles3_Ax4IwwLsZg5pU6KoN2APTbdwPJnovHs7NwWpduPnkcmwzo4A_62EilPL7kDe7FjCm7EYiWFhAkYS-SiWLtKeOSrgAtdoTRr9-Mk9jr9zee6nYET1FNak&amp;xkcb=SoA367M3jDa-65QEE50CbzkdCdPP&amp;fccid=5e964c4afc56b180&amp;vjs=3</v>
+        <v>Irvine, CA 92614</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v>finance</v>
+        <v>No</v>
       </c>
       <c r="H29" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Senior/Financial Analyst | Local only | Budgeting | Cash Projections</v>
+        <v>Twitch</v>
       </c>
       <c r="B30" t="str">
-        <v>ROARK</v>
+        <v>Senior Financial Analyst, FP&amp;A</v>
       </c>
       <c r="C30" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=7666f6a720452cd1&amp;bb=zgrb7n3lgNClGEgEYbCx_diPkm06bFAOdqTDILngulUI852JkfN6KD9YyWyV2aV_qnfdM32xHe9_BtII1rqyUm9CtcT7aXDmSCygfRGwq8dW0Sq-vVL2tZT7LDL8sE6epp2plG97GXTWkk2a2kpb3g%3D%3D&amp;xkcb=SoCw67M3jDenUNwHcp0KbzkdCdPP&amp;fccid=e21f6affbb4bb0b2&amp;vjs=3</v>
       </c>
       <c r="D30" t="str">
-        <v>Irvine, CA 92614</v>
+        <v>$72,600 - $128,800 a year</v>
       </c>
       <c r="E30" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F30" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=502c5ab7201f37e8&amp;bb=lMxi-FAtnz9DZju4Ct8nHA8brCMeu5lpL5BXJmoZDo3BiZ4iKJeRBim3qVFQt1rb1-RS9V3DNRatVJxBN6CmxdSlSz9qXegaUwvn-8vhay773XCHo_TP1oGQVmrql4Z1&amp;xkcb=SoBa67M3jDa-ZyS4dp0LbzkdCdPP&amp;fccid=ee5f7648851a3799&amp;vjs=3</v>
+        <v>Los Angeles, CA</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
       </c>
       <c r="G30" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H30" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Senior Financial Analyst, FP&amp;A</v>
+        <v>Cedars-Sinai</v>
       </c>
       <c r="B31" t="str">
-        <v>Twitch</v>
+        <v>Sr Financial Analyst (reporting)</v>
       </c>
       <c r="C31" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=b316c938981a9e7a&amp;bb=zgrb7n3lgNClGEgEYbCx_Zk2kEwuuKvwUhzgX-qPFgfd7w_Nee_Rke35aaOW5ZRPDYkmkGK3APnNBDFo-fSASn_kEmXpDcUmqhdV7DPRsBdH6XbNZa2e8EauWSo0pl-rNCGZvX3BssrzgXTSlyjYlw%3D%3D&amp;xkcb=SoAt67M3jDenUNwHcp0JbzkdCdPP&amp;fccid=22d99361dca0507f&amp;vjs=3</v>
       </c>
       <c r="D31" t="str">
+        <v>$40.16 - $62.25 an hour</v>
+      </c>
+      <c r="E31" t="str">
         <v>Los Angeles, CA</v>
       </c>
-      <c r="E31" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F31" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=7666f6a720452cd1&amp;bb=lMxi-FAtnz9DZju4Ct8nHLepbCpJLKRPpxxN-o5lgqrAh_h1WvIfPG90ZLTpe6LYcudUReHozq6bj-oxI_dj_XakEQoCO0Gu1BmUSXiFY1Q20uLuhA0Lb5z1P_IHyHFt&amp;xkcb=SoDu67M3jDa-ZyS4dp0KbzkdCdPP&amp;fccid=e21f6affbb4bb0b2&amp;vjs=3</v>
+      <c r="F31">
+        <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H31" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FP&amp;A Analyst</v>
+        <v>HRL Laboratories</v>
       </c>
       <c r="B32" t="str">
-        <v>Unio Health Partners</v>
+        <v>Sr. Financial Analyst - FP&amp;A</v>
       </c>
       <c r="C32" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=f25da10bc80f5c50&amp;bb=zgrb7n3lgNClGEgEYbCx_dJyCDW0AQB6o0854rabDqibGn3f7uhNk8gQcFbPWGA-coLfTMAV5mUTGXyRqnbtM2f8e79HyNQiDKl4cwtjAyu_pWiLuHnmkuxtfHLd2tNVN0968QdOIYkoi_xy4EWnb_FZB3Sgvy0z&amp;xkcb=SoCZ67M3jDenUNwHcp0IbzkdCdPP&amp;fccid=61a105cfbc724ff8&amp;vjs=3</v>
       </c>
       <c r="D32" t="str">
-        <v>Hybrid work in Torrance, CA 90503</v>
+        <v>$105,700 - $132,150 a year</v>
       </c>
       <c r="E32" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F32" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=c527e1990feda8b6&amp;bb=lMxi-FAtnz9DZju4Ct8nHFg6PSlo2JzUMgHoy72crDCVsaVRLUbdplXzGIGTNaUjI_L9IWg-LFj6foET7HAHY72ymuzD6xFLYi-P8mCeB7BnSCCMLjnAnJwka7FsTbuR&amp;xkcb=SoBz67M3jDa-ZyS4dp0JbzkdCdPP&amp;fccid=cfcf1008ab96e64b&amp;vjs=3</v>
+        <v>Hybrid work in Malibu, CA 90265</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
       </c>
       <c r="G32" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H32" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Sr Financial Analyst (reporting)</v>
+        <v>Bank of China</v>
       </c>
       <c r="B33" t="str">
-        <v>Cedars-Sinai</v>
+        <v>Los Angeles Branch - Financial Analyst Associate/AVP</v>
       </c>
       <c r="C33" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=bbf7bd1df4e318f4&amp;bb=zgrb7n3lgNClGEgEYbCx_Y1CgYdD76eXNfZqmwlzNzgjz5SSD0uHxzhvwO8-AjEU4nbB3e89P3K320roeRpizKopbKXCDa6EX4pFrN9yXhovGD5DCHliYuS8WOoGAd-52OQibexcn3zBc0u8iGXjbA%3D%3D&amp;xkcb=SoBj67M3jDenUNwHcp0DbzkdCdPP&amp;fccid=82a924ef8a1e6217&amp;vjs=3</v>
       </c>
       <c r="D33" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$65,000 - $150,000 a year</v>
       </c>
       <c r="E33" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F33" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=b316c938981a9e7a&amp;bb=lMxi-FAtnz9DZju4Ct8nHOX6SldUwGUMWn4KCXk64SUHmadm19t7Uwotl6qsw2GVc7rm7X5aNGWVkjcs1Is43LKhWPbFtLyN88Ai_6K48N4SQOW0yqhl0DJ0rm7cE3tA&amp;xkcb=SoDH67M3jDa-ZyS4dp0IbzkdCdPP&amp;fccid=22d99361dca0507f&amp;vjs=3</v>
+        <v>Los Angeles, CA 90071 (Downtown area)</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
       </c>
       <c r="G33" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H33" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>(USA) Senior Analyst, Financial Planning and Analysis</v>
+        <v>TigerConnect</v>
       </c>
       <c r="B34" t="str">
-        <v>Vizio</v>
+        <v>Senior Financial Analyst</v>
       </c>
       <c r="C34" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=e3251f7d064cd556&amp;bb=zgrb7n3lgNClGEgEYbCx_eO0eqbetbxz9dbysJa6ZTi-OlEiE96ImcUD9JaEADoT853QKFLn6zCfuWuo26I63w_D2sa6btcVX4pcVv4p_kvbkMm394aQvJi_0y1vsR2eznHnSNInjwOvCKaFyvPnJ75mEWpIs9o-&amp;xkcb=SoDX67M3jDenUNwHcp0CbzkdCdPP&amp;fccid=7fa25566e26b9d43&amp;vjs=3</v>
       </c>
       <c r="D34" t="str">
-        <v>Irvine, CA 92618 (Irvine Health and Science Complex area)</v>
+        <v>N/A</v>
       </c>
       <c r="E34" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F34" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=14068818e3ac2d67&amp;bb=lMxi-FAtnz9DZju4Ct8nHLzHpcrwd6XWOI6F3t43i8UIvrnJWa66efvdqYwGDsZnKT5AvghF10KBniXNu7URya0o0l4XJAgGQmOvFeL6it0z_7UuOb-e5uKBqMI8GTve&amp;xkcb=SoBJ67M3jDa-ZyS4dp0PbzkdCdPP&amp;fccid=822bc5d9a49270ea&amp;vjs=3</v>
+        <v>El Segundo, CA</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H34" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Financial Analyst, Royalty &amp; Revenue, Ceremony of Roses</v>
+        <v>City National Bank</v>
       </c>
       <c r="B35" t="str">
-        <v>Sony Music Entertainment Canada</v>
+        <v>Portfolio Manager III - Entertainment &amp; Sports Banking</v>
       </c>
       <c r="C35" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CFaPMvOM1P_0fMbRRBTFrJNGY2-gzcDaOBAgeg0Va4NEtpkM3kN69uBifdgHlvmmQ5WcQU2wk4orGBdsSZkHnQ2FGWUqG7tvDoMypN_mCgyz-xproHirqb8GQujp_T-KUgv_sNRb3khZQoZvmGDy2sLoCFFSRM8f9o3-ynNlobCLzNjMFLaFF-8X-76u7XW9x2KFsu88Ed23awK_uHD9zvR5e2bcGFJ04gEiqHGYN2S3fWB4jTaPD68MCGnFafBlQFXhJod7aE-_hfXveAPzU55D18jS8XkdzJ2wV6jYqnIYt2Chjh0XMHx7FK2C50NZeMjqCfdkWi5inYfD2VMUZVnSlzob3rW3dpoRvYGH5q__T-NjkpBbjeozf8n8dME6wXseeYInAm2v1iuQBuZq9cVchaLPFwLOEdvcO4Kiiha7uCATsx6gH66zDKAMAeZASwhsGatEG6gu9gSYvWYPwykrIKXONh6c3oQ4SO_UM31-EYGFO0m0lu2DjVMzEp-vfBvBxaaQMrHwXzPJfUI-UZkh7MAZHFXC4LCsS0_62MH-JY2EvYB_tYQmVK_pITxAfS0NoMlK4qCELdgSVP1Bbk0yeaMMTZxbcq0qjnA7xsMVwAgw0rlWKyIb8Tjpag2gCzpnyydt3lCtajuq7b4zcf5Cvoj5qqAyyjmq4WCFKQhQaTT1Ugemjk_ITPag7udvVp9k-xWfb7zXeSw5QSZD4QTh9ZIJLcEEcoWaEXyjSi3L4vghZk0FDj8Opf0h2L4RnDhTstwuZO_awueIyJjMN0aDfHSBdCy1-4sPVkGJS5gXlDv0NYcE0ru_ECur_F-vLU7Jl7eWNGvI_fvVHEd3bKS5toeTC3_FKVx10H6J76O3PjDgcKpsn9uAnV604iAfwJEF8M3Qmpm8JKv5zZelCrwvO2NeG6eJFQ4wNspmd03xA_HPMRPNsyHAFId7oA58JraZkEpX7fhFYQjyq4a9yeTwtDg29q7CjPHO5b19SR_Qzkn7dQzha8coXIuWunE8kdsMyVizOElB2CKy1I0xW3ZhElCEtGcSd_FROp0YzLfx3I595GEjRaXeb-OaQ2HcwhM8o1lN7svtpwm8kJl98igBm1tq4jT_uQAaFmKIYO_bCU_TR3m3tpCBrhmotbQswPt9vZlXcZ_7Pvgj_UKhC_aEBP-DpE0Pzu1RmFeCO1REPHwqketxhxf8g3VvpqG-hbY3qgJzB5Axiw4jjsSsUIOXAZXVcNXLKTx3XYzCuizEq31GPwLmVqfFT4d_LFDLh1-NFkmcCsrzdycnUvdtn9JmS42EbLxOL4zGjkMD--XZq-UXLqsw61sHjInp8nRxnH_qWS0IagvRzCk3FXMpi2tFhjpx0NWh2PVKtJk6l3EE1TJPs416rDUyEo-L12COw=&amp;xkcb=SoC-6_M3jDenUNwHcp0BbzkdCdPP&amp;camk=C3EPSzFlQw99czYiVxLINA==&amp;p=10&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D35" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$122,535 - $208,715 a year</v>
       </c>
       <c r="E35" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F35" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=853c2637da679d97&amp;bb=lMxi-FAtnz9DZju4Ct8nHIDpG-lKIN8U4Ps6w3OlCgvPvXFNwlo3N3Rry2e6Rop3qReJIFjCqiNj2dfKVLdcqv_TtKUA-senRQ8o39PfF4nhoZE7lItXSFJKuxbiur9G&amp;xkcb=SoA967M3jDa-ZyS4dp0DbzkdCdPP&amp;fccid=c5284eeef83d4d1c&amp;vjs=3</v>
+        <v>Beverly Hills, CA 90210</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
       </c>
       <c r="G35" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H35" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sr. Financial Analyst - FP&amp;A</v>
+        <v>Farmers and Merchants Trust Company</v>
       </c>
       <c r="B36" t="str">
-        <v>HRL Laboratories</v>
+        <v>Vice President - Trust Officer</v>
       </c>
       <c r="C36" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CtdzCyg5KMyOLBg46U32jJQpIAAtIVxOzCHrV3GC-OPKuLVDggng4aIbZ69gZp2z_jWgnYfwvuDabi2A4lAKJr6F8PYtD2ZA5GFVoLEuYBjG-rsWyzkpLRKtC5C_ja7-r8JJPGtA4zyQTa6oFS6gpQcWPlM-efwuFv4_4ah-N6wEpIV_zG5pNfj430qCzgiOdEmzGynlLVVWRNGdyWznmbK2YZhesFFKvXpuxSzT9NgMljXDhdEDQUMID3-MaC8xJxyi438BOqScjZm8lkOYN9_PaKOgKB3LxjIKhCYxo3H4bDdNVvgEM2H3qFuND52PgSt4TLcG8ohhFjmJ-Whs1YhlLlitwGm2U3HM6wCYjlLP-MPFfi_MjrlVi-EzcVZi_b77_a0DDhJ2hCany89yDOTK8YokfUrnG7KwR8FDzXQcjzz_W_522C4dX31Bq1O32gX42kjuejctjPv61_2vVDLiJ9sr4VAeAsc-ffGeucRYQ2smdWe3lOSzMtR5wFy-XSO3JIT0pWke6FWlZiljqGf1pBVIeVLC5BnCFsmqNJdtRV5qxS384oHClozYlHAioeVcyjPwLNgNRpcPmhKrXGFPlGy523zyRuTXMvt5V94TXG7mOROQa1tL9daJq42RIiySWnn2KmjxFxyqJ9Bs2J6EB-07JaXfkULOdhyC9qsLAktV9kRexsMJd_Cd8lccCdGH8QjOv6mFchhznOqzM6QggwDb4iBK9PwG3X-9ylKA==&amp;xkcb=SoC_6_M3jDejh1QrLB0LbzkdCdPP&amp;camk=C3EPSzFlQw_arLK6_BdZBg==&amp;p=0&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D36" t="str">
-        <v>Hybrid work in Malibu, CA 90265</v>
+        <v>From $110,000 a year</v>
       </c>
       <c r="E36" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F36" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=f25da10bc80f5c50&amp;bb=lMxi-FAtnz9DZju4Ct8nHNRY6reSxasgoTpFEkDFhHsdiOKnz1QDtMaMfp6doUGwqLamZcdWPa56oc_DjM2NlDfImDik_HfGyz-tKihJVS_j-RqrTnPX2wiGdpKgCMDn&amp;xkcb=SoCJ67M3jDa-ZyS4dp0CbzkdCdPP&amp;fccid=61a105cfbc724ff8&amp;vjs=3</v>
+        <v>Torrance, CA 90505</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
       </c>
       <c r="G36" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H36" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Portfolio Manager III - Entertainment &amp; Sports Banking</v>
+        <v>New York Life Southern California General Office</v>
       </c>
       <c r="B37" t="str">
-        <v>City National Bank</v>
+        <v>Management Opportunity</v>
       </c>
       <c r="C37" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0BnmKIZ9zMUJtlD2q-PunJH8f4JqZcGSyf1KXmaJs7P7XcG4oHTjupAnGn6zrwN0IUW_G_l9kcjuau61g_XlGouFzoR9RehEpWXFbsMB5N6eGRR3d1oor8Cd4aAAm3__UBP16WGGf8t1jjq0BX4WsN27zV_sMeIhQqnPgYYvzoRZoyfE2hAsmrP-hAZh-JPYo2FFussD-UTCPDs8DM-C5RAat22fgKJVpjK_Ol-B3oEJCpVC2xj4DtnxZvQHIbvM68Do1EhGp1VTVCwly3WM5mbQHBvwlsubTg607zNeKVDWFw1IV1dHnUhdXI1Tk_JCOakk1VC4CbIUA3IgmHSrdz4YIwwnDQ4hfAyV1TGGwTz43r0twRfQUVhWRAF6LIBqUPgumf5iJwwxI03hfy3j0zCdhCvUG5EZ6HQYtA8bENJwnohcNGvXvzHZrzslXsG6XIJMa7PD81u5j-2lrdRRaCgGCvV6Ct6FFY2ChXRBFLz7WTt-87TokEzNLOcy-35IgdHQLGcTaRlfCf1ALgZNaKqaCpsJ-Bpm0aO9tSyMwoYvr0tYxzVxtb_ylVQRUSA968hHBm51yfJLKlOzswkJXkN8MLFQqyyV2zyZZXC8lIs7Nv1c5lPCQw2Isb3ofoVQQ0Y17gKeb-xil3EBqMct9LuNbeEXgiLPrJBkBmGx4w-3e0etwi-9BW4fCGixl0W6wU9oScM--R21YalKidQuGxA&amp;xkcb=SoCW6_M3jDejh1QrLB0JbzkdCdPP&amp;camk=C3EPSzFlQw_7YE67CmVMaw==&amp;p=2&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D37" t="str">
-        <v>Beverly Hills, CA 90210</v>
+        <v>$60,000 - $119,917 a year</v>
       </c>
       <c r="E37" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F37" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CFaPMvOM1P_0fMbRRBTFrJNGY2-gzcDaOBAgeg0Va4NEtpkM3kN69uBifdgHlvmmQ5WcQU2wk4orGBdsSZkHnQ2FGWUqG7tvDoMypN_mCgyz-xproHirqb8GQujp_T-KUgv_sNRb3khZQoZvmGDy2sLoCFFSRM8f_oGOdLYHQp_1OlORNkmisIwSrdpU_Fr6uq26x27tB46bdHGARP3cF_432YJNl-bnN-Tcu3TXi-4BPFTARUWQPTJNVPP8CF2l8OjVBCjII8ztgFEiI9f9qGU4Fn6wS-hwyW8obES2o9JThC8f9ppKrjakEaB4oMszA4EnaWLnqmEAE2op1hPmZst8SbFvj8pIhqdNmHlk06LBLa8ILhl825xeGbWMTy42Rk0ZPW48fD4sTuY6CGk9Lk5trp3yOqBw-EaMKOZj_IjhdhzXcOMQFN2AjBtAAL_bcGiZqhERumPyxSVsSMD6VMj0B-pMQpsvai7AEQQKVMrOiCnHPRh-NsYJAccUXbvZs4gYFOazirXbh7jjHCVeHt75tAADPOp3VPXczq3IA0D_9ckOBimwnIbNVFJRRvmOT1lFQ5h7nEUHdGHyY35t62sCbG4T25aSMrfbFpCnX2OiOvVhMCNoR4yNvgLPqaQqzjkuLkM0rZqesaFYaU7PgqG50QxUsMlbJxOtgu1w1feS53Edl5RFbukfDaPrCV64qoDmEaOSTWs5Ty_VWq9xpEPfcK9XSCWpmzs_S5qJptOYwSv0910dRYCMMmSjxxq91F1eGaa134DVe7AdhYMN77ojmFC1tEN9Y5A80yktcmSsDcAq5nJO1JQ8LhaLxMQzAl-KoAHGxn_sDPrrBy3b0G5KfgNZnu2SAD093T0d48tGMoD5LlD1qk9c6l126ZTNtuwMVGNkJzUMETZyyN3Sqzi0bG7NemihEtRLU-1N5szZynBgIBaLWQ_npRfNtlqpBOZk2VotuQ4JOt41EjnWp63hSynHV3whc7I-dtRR6UHoJitgOH8ZeXtJSPX6Vko5XcpTRrLbRuBEZJiX-z0pWDM6_g0d6a2hQncNruEQIuaefqv_jUfw_oND4YNzEg0-IJrg1uZ8RdLIaVqd_0C8R7rfwHGUjPQg55y0ToTsQvavnt6Xo1ZAMyo4KnAt0du-RD7ZzjHFxvH45W1VREPfjElsKME-k4AKvh3CUubAKTvqTDDit7ERad9mNvvdMZJM3T2JZEDYCA-2JG2l-j_Ie9fm9YhC-uLJZtOF6bBri5L0QafTbbLvXHJoosYpPQY3x4m5UWPphuR8VurQ_hHS-fCIEF3TnrM2Kk9Ehf6-nNlatXixK0SnN5nhjlcUrBuTzTS3BgFqocb7Cr9PrqpNM6Q5rPXjMJiDbOoKygXugUelOW5S37oD45yI2YwuqlEaXRHUq1Eha6RA==&amp;xkcb=SoDg6_M3jDa-ZyS4dp0BbzkdCdPP&amp;camk=C3EPSzFlQw99czYiVxLINA==&amp;p=10&amp;fvj=0&amp;vjs=3</v>
+        <v>Hybrid work in Glendale, CA</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
       </c>
       <c r="G37" t="str">
-        <v>financial analyst</v>
+        <v>No</v>
       </c>
       <c r="H37" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Financial Planner (Los Angeles, CA)</v>
+        <v>Fair Trade Real Estate</v>
       </c>
       <c r="B38" t="str">
-        <v>Mercer Advisors</v>
+        <v>Real Estate Investment Specialist</v>
       </c>
       <c r="C38" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0Bl3rZztmYuXIIuiauf0fa70dIDzRG7j9AV198kgg0SWztpClYvM_lVFrp8uMM29HlrpDaxsd15MNKkLaEarag2qtrUQEriHMz62Mrp4PLEkH8cOeB9mdLktbO64xiia-JtErv3-gGctpcojlnzlzt-3OfAlH6uldKitJGN560J-zGAKKbSCj6v9PiFzFFF2QPnNpGXht7NsnB3VoTezcYpK7yLHnW6AbRVWtwcvyZLb46pkI3EA9kiY0wyIV6hMr2psUyYjzGkRiCO1wRBC5lwP7YdbB2kCsaaMfOMVe1D7cKFOY3QXIis3puldD7T6J6Fn2feitNxjKXrhDsRzhymfcvOUSTzqjeQ2wHzd9Cgfv-dOaovQbVSCASAZqq_qO53z8XceJ4gC_o8vgcvbCjCBL8nYAdb8LhV8gKfdp9hp8ffFFnPFdQVHw0NmefMLabgDih7WhNbk70uodYcHj1pRIw4FCf34OdvsKEiZY_9rn1ijPhlLVQClcXuq5OEHz6IFh3_h8FOwVW619a4vRhEaqT6rruuTMCkslaQW00EzBifJ8XNMcGp4kyf9XV2kXWk3EQr-8UoxI5e3YzPPonUdj5rM_fqyFrG3H8wp8dl1_7YFSdBKuIz6B20vfRKLVoTcSc4EYGFs-JJUPV612ezG_379MVUPAAlMIgl_qfyVchX8ZYy1j353qOzLdpO8KflMfnBDTG6T5Y73sqx5SNgdks26-Dgj10=&amp;xkcb=SoAi6_M3jDejh1QrLB0IbzkdCdPP&amp;camk=C3EPSzFlQw-FqUHjS10VEw==&amp;p=3&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D38" t="str">
-        <v>Hybrid work in Los Angeles, CA</v>
+        <v>$100,000 - $500,000 a year</v>
       </c>
       <c r="E38" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F38" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=4b75d4c6f7349293&amp;bb=LxZnDPzr9KNJLDCD64zDo2D0Tg3WG0XisfsctKoaXgkm4-D4ljNCKD5WPvmthjyDs5M8J4X6GoB-DQ-AtxrXE23CT5lQKRWUwTqZy1Wo6gCzCmAtlzsVLKPaM6cgnGjFaAWBIhrQpwIsiFR906JfHg%3D%3D&amp;xkcb=SoBO67M3jDa95NygH50LbzkdCdPP&amp;fccid=30eb012d7aff613a&amp;vjs=3</v>
+        <v>Hybrid work in Irvine, CA 92614</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
       </c>
       <c r="G38" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H38" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Financial Planner</v>
+        <v>New York Life</v>
       </c>
       <c r="B39" t="str">
-        <v>Compak Asset Management</v>
+        <v>Chinese Speaking Financial Service Professional/Financial Advisor * No OPT</v>
       </c>
       <c r="C39" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0BRKb2Yl2tKYxOGwb4-47fcXnsSLbs6s9iLvBeV_nUgxUhaMyN9bL30s1C76eZs9AxLcwqsTT3jZb3P4wVnuZ1yA5Klaf-Q4rh303e9-knL-K7_1c01K5zTpgSE0j4NTm_pyNow8g3DNo3wjV7qXDfYQjBso8SYjwJzNpZ0mkp3jLAeiP_2AojRYss0LHovJWXQSG1kT5EwHGKb52Bt1t-7e_vkVr2DOavvFSDBQ1Bl12BwBFLK4s4EmUxlcm6ZWzmCB3zOScdDbXp_Z7dJtSxa7z3JoPUZL9gBu04o2SaI2kF3mZmriwcOXT1uLyjLgUN0bzpy9fBXaqzMPW9E_Xz34g9iAG7JxBj5z206fZtEyiGJ-1YtMOW56bbgL3aWXqIEYB6OgXDmB6ufEnMS0t3-Rnj5eg5ipdUyynepv5BINzwO4Aq984G75donLqD-WjrZLO94P1v6A0DhFVC7tABE3Fk2r_wAg_GELo70mO0Mkmf5P6bguSnNhbcoISU4J13JsXopgf0K6AB2dOoTb1fsXGMYE-B3ir4QznL-dad6onkEK92N9OoD2bNCKn5Z5yttwyIhdQGn9WMi_VnK3UpolNTBkX2gs9kh6RlXY5fM7t5ee7HYD4QHCu_FQJOxOP36HxiRZ_NRzDAhUIi_Vg8AQP7a2zD8ujAktOFUtdZBB1QJcN-Kyuw3AFVPGopXlkpUnbrxMoJ-6ynC3udBz5ante3lIujfY2dzuBgYlbxeCwTq_hud8u4SZ7MvEL4-wRamPPTndOcT5A==&amp;xkcb=SoAY6_M3jDejh1QrLB0ObzkdCdPP&amp;camk=C3EPSzFlQw9fCHh11OrhYA==&amp;p=5&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D39" t="str">
-        <v>Newport Beach, CA 92660</v>
+        <v>$60,000 - $80,000 a year</v>
       </c>
       <c r="E39" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F39" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=a7ebbbaaec2dc98a&amp;bb=LxZnDPzr9KNJLDCD64zDowgjOqnjXKb8m3mEJn1pjyYgBa9u3IhF-38RSa-Mctbfr6wGQ8jRNBTj7eC-xO-92IjMa3Op_SAyaKngyC0vxb3dkMIE5jfJ7oh_CJDJbC6PceFsMyKbhg5RcXEa9G5vy3ufTAkLBtg1&amp;xkcb=SoD667M3jDa95NygH50KbzkdCdPP&amp;fccid=205ec86ddf37ffec&amp;cmp=Compak-Asset-Management&amp;ti=Financial+Planner&amp;vjs=3</v>
+        <v>Pasadena, CA</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
       </c>
       <c r="G39" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H39" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Financial Services Representative - Santa Monica, CA</v>
+        <v>Centennial Advisers</v>
       </c>
       <c r="B40" t="str">
-        <v>Fidelity Investments</v>
+        <v>Commercial Real Estate Sales Agent (Entry Level)</v>
       </c>
       <c r="C40" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0D71Bx9aca8E5YUHf_Ru6IiaD1b1Eh66cyKIfbmm8FoeNnjZFcKiQ5KD-BFXzNLY-I9XwX9gYeC3CJOshhDbtV411AXIlweipPPi5EZ_WsoLuf6t7aoJI8ehxJo6pSYcxjrV73vK3u7uQnn8yc-7gqj0szeBuSi386pzZUSuHnxeZIlxo09E3B2bku0SZIQmieQanuAGxjJnn8McW5gebVRPFklTSvUBvQToaTOGBhEdI3FsklHpJWUI8lhBxjz_JcsIY8RQ_U9seD5J_M5an3laLMeE6oUr3E3GKKDsn2-tVGlI4tldpHzzCfxkU5swzrBGYvprmDlTB2xBPsXG7XKGK-ybicGTEG8IbfGyFdVUePDYrKd8TKZ68Bqhks6jEKAKXhh0jEpjxLSe1veW8OmNevcAqvkxaFOq9i3JQLAzANmktXI3J2PxGGt9LP1W-vxxQti7g8uolsqY6I7dOIL_Y6JCkIDRN6AE1M7PFf9DgLy6uOWnWl9mRk8Y94QQJhdGZLV0vxR0onXWd4cMT-pzGaJddsmkyjQZhytFPmotKPmNiS31h2kQAkYPwI8-gUaxcIXbruRx_3NIy6N6noatcrvAJaOYX4bulSlylpE_xvv1EYLv8XpQ9ceNAWZNsKb2i1DZpcAw_pzVt_8uK_wKoJKLuIs17QyszzH_Y3e-Kw8bLd4TceCphceLc2JanXgwsTmgvz9MRnM1XrEgIRRRJH2cQYnoYgI-uksDx8OWw==&amp;xkcb=SoAx6_M3jDejh1QrLB0MbzkdCdPP&amp;camk=C3EPSzFlQw8GKYsMgZ3Img==&amp;p=7&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D40" t="str">
-        <v>Hybrid work in Santa Monica, CA 90403</v>
+        <v>$1 - $300,000 a year</v>
       </c>
       <c r="E40" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F40" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=7c7c88e68a0ab71e&amp;bb=LxZnDPzr9KNJLDCD64zDo1O6jyLH9ySWYYrhlL3AlfzRTMqkDnqfp3FAp9DBfoycXWTncwRA2-3ohb9Vz-8f0WYeWMqwQjz4ozRYfcCsJXAbEAu3PueJHh5V54AVLFgcRJuS_Tou4Ak%3D&amp;xkcb=SoBn67M3jDa95NygH50JbzkdCdPP&amp;fccid=deb234f9dd3edcea&amp;vjs=3</v>
+        <v>Los Angeles, CA 90025 (Century City area)</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
       </c>
       <c r="G40" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H40" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Wealth Advisor (Torrance)</v>
+        <v>Deloitte</v>
       </c>
       <c r="B41" t="str">
-        <v>EP Wealth Advisors, LLC</v>
+        <v>Investment Management Business Strategy Manager</v>
       </c>
       <c r="C41" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=fa9d1ad358a9056c&amp;bb=FAP8i5927CyBQjauvYDYuvQwQutDp6DGk5KLcMJYDUG9-4sJ9UWUe_e0AVeWRKU-Qeq7T6zBNr9JX3FDRHxGHRBZlK5Yb_YW7hWdgdL6Mwf9JQ9dE4pakN9ePWJrN_BImMJSwk9DZH0vXRUBpv37TapS1JMLYN4i&amp;xkcb=SoDD67M3jDejCMwvzZ0LbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D41" t="str">
-        <v>Hybrid work in Torrance, CA 90503</v>
+        <v>.mosaic-provider-jobcards-1oa1vqn{display:-webkit-box;display:-webkit-flex;display:-ms-flexbox;display:flex;gap:0.5rem;-webkit-align-items:center;-webkit-box-align:center;-ms-flex-align:center;align-items:center;-webkit-box-flex-wrap:wrap;-webkit-flex-wrap:wrap;-ms-flex-wrap:wrap;flex-wrap:wrap;-webkit-box-pack:start;-ms-flex-pack:start;-webkit-justify-content:flex-start;justify-content:flex-start;}.mosaic-provider-jobcards-1oa1vqn&gt;.ecydgvn1{max-inline-size:100%;}.mosaic-provider-jobcards-1f1q1js{-webkit-flex:0 0 auto;-ms-flex:0 0 auto;flex:0 0 auto;min-inline-size:0;}$144,200 - $265,600 a year</v>
       </c>
       <c r="E41" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F41" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=bc1366de3a90d90f&amp;bb=LxZnDPzr9KNJLDCD64zDo5mkQdjGmfU7MhQLo-OAzfRO7aNaVhjP4N8fOOl2EpZbEmC5x8CWEJV6wWKOy69EIiAsq6C5mZ4tOLjHbQOn2hXR1EQa0F2mwRk1wMaRFsTMvovOa7XApolBJj8MMXnKnQ%3D%3D&amp;xkcb=SoDT67M3jDa95NygH50IbzkdCdPP&amp;fccid=003f6761d5bf12e1&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
       </c>
       <c r="G41" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H41" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Investment Banking Analyst</v>
+        <v>L.A.Financial Agency</v>
       </c>
       <c r="B42" t="str">
-        <v>MUFG</v>
+        <v>Hybrid - Accounting -ACCOUNT MANAGER - Entertainment Industry - Encino, California</v>
       </c>
       <c r="C42" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0DF59-JrgplcDZQQxOVst2JFx3-9yq5CFmnl0ZDrTt8Syt9vJ_8cU8lhH7Q6DbAI5M58dWYFBQ3WacMhg_AJbLGSkX1rzujPxUy3lpeR12U4dCMo1t6MISuIqIhp-R8MabWlC62KZ80AldfSr8D02_85XLZch5xD1ZRGG9Hf-omn2enMAE84TD7Zs_NTgAe6zAOq_4an7GL4RDE1oAYO5GCY1HVqMOs6oUaSU9U-xByNWzpz9FoMLZx2sY-aQG9UEXWqEauhsckzEyKduBIFcPa0MzwCtseLU1EDUVYhwHPFsFenRCAV1J8dovJyy15ZIGQzHeeRJGJLkk3mmXoTYUi_E4lfgfctpx9brK3FJeEBaTL2Qci_-SiMAnIx5VSXVTFEnqT4trkSF_cuq6exAU1a4yhby75ssPqW48EQhV955KujMOmh3A1cW_dKdnD3ADhcK8EDdlOLstXJKUred27ZMV5tHtPTU-Rl5bnxbghxr1lhkYrGQOOYZWd-CKKdzDI9-lvcTeLaCRqQyVJbn7WhX8q8JgZeV5IKKN3EOAvBeUsDaUqM2jhtV6a5aHvbPfp4Nu4Ob6TPMIsukXtbR2b9TnJjn7yjKkqgAKfdN2sAVtoAzv6-hqIMVl19UGkRTkWtGdS6c9Y2YqKzE8ld023pn3R1rxQLlQzxt-FBA--WaQXdfYv4g9y-aRjXveQgF2vEPVuiu4DsBwEJmFMPcJO51IhRm9GfLFkoE-rBBYyOYEXGMwhJX5REUhtMjtYkZ3Kf_FaMshhdX3he_Q5mNPex5_hR51iUtk=&amp;xkcb=SoAe6_M3jDejCMwvzZ0JbzkdCdPP&amp;camk=UoKtGZLa3XKQomOaFJrmcA==&amp;p=2&amp;fvj=0&amp;vjs=3</v>
       </c>
       <c r="D42" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$150,000 - $200,000 a year</v>
       </c>
       <c r="E42" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F42" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=458b8b10839b5845&amp;bb=LxZnDPzr9KNJLDCD64zDozPbXRHAqVfYpvj2xngjvq6sSQ2CIMVOuM0SoLfSCawfDbVA3exgWduFWXRd2mvy6yfHnBMvVJwPLVJi7VQ5U4xWByixYY0-P51GCik8fjc6vjg9yKyM8_qwlktu-hX99Q%3D%3D&amp;xkcb=SoBd67M3jDa95NygH50PbzkdCdPP&amp;fccid=3b98171e4a0fd997&amp;vjs=3</v>
+        <v>Hybrid work in Encino, CA 91436</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
       </c>
       <c r="G42" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H42" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Investment Management Business Strategy Manager</v>
+        <v>Deloitte</v>
       </c>
       <c r="B43" t="str">
-        <v>Deloitte</v>
+        <v>Payments Product Lead, Banking</v>
       </c>
       <c r="C43" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=8c307dd61c65478c&amp;bb=FAP8i5927CyBQjauvYDYuhOZrpWeuTXjDduZH5cHGXpq_RvU77BmNSs72wgRYu6Xzyatb8EqQ6JNlIfgDTkTP4ZtD_-GWZBPnenkWFxgWxB5Lhz455jT_ust1XJZs_jbqZfdWOI0No1yFeWLRSOlaxort1kegUY8&amp;xkcb=SoCk67M3jDejCMwvzZ0DbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D43" t="str">
+        <v>$118,700 - $218,600 a year</v>
+      </c>
+      <c r="E43" t="str">
         <v>Los Angeles, CA 90013 (Downtown area)</v>
       </c>
-      <c r="E43" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F43" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=fa9d1ad358a9056c&amp;bb=LxZnDPzr9KNJLDCD64zDo_LntbLE-Ca6mpxKIsZPF0DJc9X8fqSRTIUaMy3Yl1iTF90DJf6qszL1WIGwaDm4Wi6PIa74eoaL9L_TIAWj8zVPg3l8pumL5PdtKlnIZIrnAfw8Y_65g20%3D&amp;xkcb=SoDp67M3jDa95NygH50ObzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+      <c r="F43">
+        <v>1</v>
       </c>
       <c r="G43" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H43" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>Panda Restaurant Group</v>
+      </c>
+      <c r="B44" t="str">
         <v>Executive Director, Accounting</v>
       </c>
-      <c r="B44" t="str">
-        <v>Panda Restaurant Group</v>
-      </c>
       <c r="C44" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=c211e546d109c2dd&amp;bb=FAP8i5927CyBQjauvYDYup15eFxvK3KnKlXDlaPL77_F85nhZNkXJvvFdH4UwQPWtv8MxUUOIRDg9Uypu-iOJMCF1H-Vjb8dls4t-XgucxvgFRzPsPLL5wkpCLom3ZivL3vciqCh9ykNZvZ9_hKG8pKpvceVLTeo&amp;xkcb=SoAQ67M3jDejCMwvzZ0CbzkdCdPP&amp;fccid=f90aa7b6385c5a56&amp;vjs=3</v>
       </c>
       <c r="D44" t="str">
+        <v>$205,000 - $288,000 a year</v>
+      </c>
+      <c r="E44" t="str">
         <v>Hybrid work in Rosemead, CA 91770</v>
       </c>
-      <c r="E44" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F44" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=c211e546d109c2dd&amp;bb=LxZnDPzr9KNJLDCD64zDoyOrwkfATMXZtRJwa7Ujs0t4hlgtkYXiJDlqbsRzN7-A6qdn6j7omIZ6O5zvqTd8EoFXxS39iGy1NHiWWl3KtUndbKxJUk2F_PV7MFyjk1epHxmoae1cbZQ%3D&amp;xkcb=SoB067M3jDa95NygH50NbzkdCdPP&amp;fccid=f90aa7b6385c5a56&amp;vjs=3</v>
+      <c r="F44">
+        <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v>investment</v>
+        <v>No</v>
       </c>
       <c r="H44" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Director of Finance and Accounting</v>
+        <v>JPMorganChase</v>
       </c>
       <c r="B45" t="str">
-        <v>Marriott International, Inc</v>
+        <v>Branch Manager - San Gabriel Market - Alhambra, CA</v>
       </c>
       <c r="C45" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=2ca5847017254786&amp;bb=FAP8i5927CyBQjauvYDYuhTpj3RPBuiyIJkBfGGEcuBW6Jj8vUP-Y5iKXJf0ntKvEKvdhtNZyhy23ed40s9atc0bTWtIaf0-JK-X9-a8OOrd1oMhKOWjW5beAE9GavKGLI0iVCIp1twjFRj7uLMnNj5rG0zouETq&amp;xkcb=SoC367M3jDejCMwvzZ0HbzkdCdPP&amp;fccid=c46d0116f6e69eae&amp;vjs=3</v>
       </c>
       <c r="D45" t="str">
-        <v>Marina del Rey, CA 90292</v>
+        <v>$38.46 - $53.85 an hour</v>
       </c>
       <c r="E45" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F45" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=28f1d07e8aabe5e2&amp;bb=rxxItaP-HFYSKkLuoF_GmQDlUBHEGOy8GlcStIlvcPzgJSRJDRjt7ZnyYh8giw9exgI5Eh9mzMW-53vbfpg7tgmOMLgwFdGNBWIW6mdeMBbO0gx7iy_evXUERNvl4vw0BMYy_d0n0QIaaWAu4t11kTn1x82Wk8aD&amp;xkcb=SoCP67M3jDa9ItS4bx0DbzkdCdPP&amp;fccid=0b6c496064ecd79a&amp;vjs=3</v>
+        <v>Alhambra, CA 91801</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
       </c>
       <c r="G45" t="str">
-        <v>investment management</v>
+        <v>No</v>
       </c>
       <c r="H45" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Manager / Senior Manager, Financial Services Valuation</v>
+        <v>Amgen</v>
       </c>
       <c r="B46" t="str">
-        <v>KPMG</v>
+        <v>Clinical App &amp; Analytical Services Manager</v>
       </c>
       <c r="C46" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=4a680d453be6b7e7&amp;bb=PQ-m78XuRaU_ZYcI94u7J6lY8uFXkYL9gzNwTrdfynVreKWIPkSM96UMCqnH4TdtOQX5LRXmkOljSGdLhRoeop1Fryzc2fOCqc83UocpF3_Twjk3K5T4rQff9GPCfaEB&amp;xkcb=SoDR67M3jDeiu-QEE50IbzkdCdPP&amp;fccid=ec34037a9c92d805&amp;vjs=3</v>
       </c>
       <c r="D46" t="str">
-        <v>Los Angeles, CA 90071 (Downtown area)</v>
+        <v>$130,065 - $155,856 a year</v>
       </c>
       <c r="E46" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F46" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=311c9327faeae318&amp;bb=rxxItaP-HFYSKkLuoF_GmcY35LoNNU56OiWl8hV6JiFp9ObkONcvkxd7vW2hpxFfVVZvjRaqNg-HHW36rJ24mKKqKEVJ5NFc3DCxiQTLSieEYWaDWWrBSLILf7dPzHaWHMS1v2l2Mte21-qqS_WJ_m1M9GdJV9yZ&amp;xkcb=SoA767M3jDa9ItS4bx0CbzkdCdPP&amp;fccid=2dd390c3a48a7ed0&amp;vjs=3</v>
+        <v>Hybrid work in Thousand Oaks, CA</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
       </c>
       <c r="G46" t="str">
-        <v>investment management</v>
+        <v>No</v>
       </c>
       <c r="H46" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Sr. Relationship Manager -Global Commercial Bank - Middle Market - Technology Group - Los Angeles</v>
+        <v>Amgen</v>
       </c>
       <c r="B47" t="str">
-        <v>Bank of America</v>
+        <v>CD&amp;A Data Scientist</v>
       </c>
       <c r="C47" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=9161a6fb29357630&amp;bb=PQ-m78XuRaU_ZYcI94u7J_4a-cpTnbmrzUbpqpvK93rUlzfEa_rXnZovud2dt4kqN5X1Y87XngoUIRyKhU3gS8qsDrBlr0T9QF3mK3X2e7ohBhHtvW4NRP7Q1iG6m4RG&amp;xkcb=SoBf67M3jDeiu-QEE50PbzkdCdPP&amp;fccid=ec34037a9c92d805&amp;vjs=3</v>
       </c>
       <c r="D47" t="str">
-        <v>Los Angeles, CA 90071 (Downtown area)</v>
+        <v>$103,852.15 - $140,505.85 a year</v>
       </c>
       <c r="E47" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F47" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=cf5b5f31df7616a0&amp;bb=rxxItaP-HFYSKkLuoF_GmZD5pGIco_dtL5FE7glfCqEvv7n5bxOqEsxPk8nGQ7KB4aLzKXsxjBugTO8p5VmOLn7T5qGlvgt6KGbcSz8cLXh5gWfqA8ZGr-JDprhZ9r25WeTJL8fJbFrSO6PRsodl0mB6_nigOxrv&amp;xkcb=SoAo67M3jDa9ItS4bx0GbzkdCdPP&amp;fccid=5bd99dfa21c8a490&amp;vjs=3</v>
+        <v>Thousand Oaks, CA (Newbury Park area)</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
       </c>
       <c r="G47" t="str">
-        <v>investment management</v>
+        <v>No</v>
       </c>
       <c r="H47" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Machine Learning Engineer, Sign-Up Flow Optimization</v>
+        <v>Northrop Grumman</v>
       </c>
       <c r="B48" t="str">
-        <v>Paramount Streaming</v>
+        <v>AI Systems Engineer (Principal or Sr. Principal Level)</v>
       </c>
       <c r="C48" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=f08babe97b1a3e7e&amp;bb=PQ-m78XuRaU_ZYcI94u7JxFL5CAH85TeRCqBW6q7kbpf8FBeL0qPkb4ISyLD7G0TLv--C6vHw3F7CtTDc67Kq-hOEkm83ppA2oTpnfz-oyh5BUAekKUYE0ZT0peaZn_5&amp;xkcb=SoAJ67M3jDeiu-wEE50LbzkdCdPP&amp;fccid=11619ce0d3c2c733&amp;vjs=3</v>
       </c>
       <c r="D48" t="str">
-        <v>West Hollywood, CA 90069</v>
+        <v>$137,800 - $258,100 a year</v>
       </c>
       <c r="E48" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F48" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=bf75e7ace01e5bff&amp;bb=hXm0SXSCybqzMECR4SNEW2XI8Su-wg-Pbe5K6azgqqiEcVk6LZTptw9oJQVrtUhrEbKW8pEQr4rPHgLniWadcUw9Aup0PQ2lucxTmvMnVA7awC0lJvO9XP25NGDBbGrz&amp;xkcb=SoCH67M3jDa8XHQHcp0LbzkdCdPP&amp;fccid=8364a618148a6cf6&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
       </c>
       <c r="G48" t="str">
-        <v>machine learning</v>
+        <v>No</v>
       </c>
       <c r="H48" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Digital Product Manager - [AGILE, AI, Stakeholder Mgmt.]</v>
+        <v>USC</v>
       </c>
       <c r="B49" t="str">
-        <v>City National Bank</v>
+        <v>Clinical Operations Business Intelligence Analyst (COBI) - Value Improvement Office - Full Time 8 Hour Days (Exempt) (Non-Union)</v>
       </c>
       <c r="C49" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=9db9f1aed0caa4fd&amp;bb=ptVQyeMHI5dXXa3N0XapwUsT6CADgIs31urnZ-m8t4YzH2HIRDzGQlWoNkQ2gvfDuYV_v6fpUqcw6XezZXaVJUEPwDd03ljsWZr_Caxl8iykWYzu_K2qiOWIG0TvOZ3p&amp;xkcb=SoCN67M3jDe_E1QEE50LbzkdCdPP&amp;fccid=7455773bace145da&amp;vjs=3</v>
       </c>
       <c r="D49" t="str">
-        <v>Los Angeles, CA 90071</v>
+        <v>$81,120 - $133,010 a year</v>
       </c>
       <c r="E49" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F49" t="str">
-        <v>https://www.indeed.com/pagead/clk?mo=r&amp;ad=-6NYlbfkN0CFaPMvOM1P_0fMbRRBTFrJNGY2-gzcDaOBAgeg0Va4NEtpkM3kN69uvUbQwEDOOix5uMqZbnWif8swRYREyFHyzEwuSg5nVfdLMUBqhSEFGLKAia-kPM5vAVtt9uCZA2RrRiLTQ_hY4cTO5g2EwpL6dtftFRMUlayPODtrKRNHdT2OFedtglk7F31YxXYbJff80_1BVQZhrScrZtQvNZpcxrn4ODyKWV9CQrWqi9c6_koEdx833cQ1c8B9kovjR-XhXnC2AvZRBn3kPyrKztyQ538zMmaiXqgmfcK9nv6tbcCHzYKlmc_LSTnQdh6cgg-4kfOg3ucyUe9SK_jkJIgjTc8Ply1NPn8z92Rb_Ki-PmSJ_E0pYolRiY6GliKsm5m4sA5fZhZhcdzGtIZHwPr-HhVRdlM5uf0CsphwNKQ3oTW1b964WyUvXQNWBWSJNkl_AwW7mnfA7RWTiNGKFuCTiGIzTPnBSjSwC7zCVin32HXhxDG39GYeUgctIa9cw1Hp3vPY1U876NoT-s_ZCSF5PAiMmy6eSoAhV5nhMLI8D7EDNKph12T6XHT1GO2eaUd6yVWtarmDsiKp16DWRwBhBUdqTHaDBdfer5lM601GdJJ0rN_gqUf2IzGCo6CLgBl4kLYkdsgCVV01y6ZrDYU3J8UdYcacQEECTeo55gU0d4l51ByUPv5v21NGa0Y6fX-_qGCEmF7FZo8qZMZZkzdHfWDc2pOO0AKbEfyBvrbv7JylF5o2FYdk2jUHC-sTfQzX6uL_VGoSkZBCQOCmMxBP0UF31ayOqpBcsddx3ZO6eqiJCDIXb8w-rbqMcKzzH8m8RwCxCWPGHW6qpSs55TBxULamyS8ApIcGi_afhkujgRceLv052x4EiH3kFQKWjQopBpS5TcoZtGPnWFVwDHX8e4rF28L9-NDSGfya5vARI0NxvyKvB3lWhnekU2TnuRBc3wzpH1IcVEseCWni7AUJ4-4Iy-QeTFgs_0Bt8Z7ktNL_yystwwajULLrqRUPYR8-lsZ7SiUSXM5kwDggDQfYe7C59dw3oikNlkakqGu79BpVlKRbo4jRr_VTFwQu_Tee6IzcrE_Jfa1ELEYeLjtgIsO4dDQTo7R21V9P7uEqs4KWhIlai0PsXyun-wFRSPSAbeppKc3yvGwlFUO-4H8gPUeFVTgFqOSs2eC8KQ8gmx7gqu5NP5oaobJmlHJL_3H1yGjomFVpTa9Myb0qs-9DFU_iNxDpuoca23kQuU0otU8gzykY5kprt5yGuDjjRRVMjZZVtZAPy7tySFZ449gYA42I1YxCXCeOu69FoaOpjndydT7cuNCn-3fPO8GijmmTvUsSCuEMNql-apJQYcfPKtiMd5PudjrAbry4Is0yMA==&amp;xkcb=SoDH6_M3jDa8XHQHcp0KbzkdCdPP&amp;camk=C3EPSzFlQw-Md2aBnTjMvQ==&amp;p=1&amp;fvj=0&amp;vjs=3</v>
+        <v>Los Angeles, CA</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
       </c>
       <c r="G49" t="str">
-        <v>machine learning</v>
+        <v>No</v>
       </c>
       <c r="H49" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>AI Systems Engineer (Principal or Sr. Principal Level)</v>
+        <v>Heluna Health</v>
       </c>
       <c r="B50" t="str">
-        <v>Northrop Grumman</v>
+        <v>Senior Information Systems Analyst - Cloud Specialization</v>
       </c>
       <c r="C50" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=6c1b66aae8e310f7&amp;bb=ptVQyeMHI5dXXa3N0XapwdwzdSW60dk04At3H5_2sEpNDvna5MqROvzPfWP3e5ht12mrgSk44JJFmkL7sEgEgYbiO5FSozAABi0yUUcAQkOT5oXt0lATq_TtPDDds2Ku&amp;xkcb=SoA567M3jDe_E1QEE50KbzkdCdPP&amp;fccid=b27e6fc6d7424c31&amp;vjs=3</v>
       </c>
       <c r="D50" t="str">
-        <v>El Segundo, CA 90245</v>
+        <v>N/A</v>
       </c>
       <c r="E50" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F50" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=f08babe97b1a3e7e&amp;bb=hXm0SXSCybqzMECR4SNEW1rx_RE1ZnymrQqkf-kr-Zer6EifWmKsLawQe_0VwZq2tlAjSa04s4Et6321a2w4zDuTEgZUtmZ1cKCb2eBmK--2FjoSXpFHqOY1nqfS4mLJ&amp;xkcb=SoAJ67M3jDa8XHQHcp0MbzkdCdPP&amp;fccid=11619ce0d3c2c733&amp;vjs=3</v>
+        <v>Hybrid work in Alhambra, CA 91803</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
       </c>
       <c r="G50" t="str">
-        <v>machine learning</v>
+        <v>No</v>
       </c>
       <c r="H50" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>AI Systems Engineer (Engineer or Principal Engineer Level)</v>
+        <v>Wescom Credit Union</v>
       </c>
       <c r="B51" t="str">
-        <v>Northrop Grumman</v>
+        <v>Workflow Systems Analyst (Anaheim, CA)</v>
       </c>
       <c r="C51" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=5dfe0d094be4e7b7&amp;bb=ptVQyeMHI5dXXa3N0XapwUIxb7i4-uKqqYR0D10B1GX61y6039bcyZIi6DgNDJoJKldI7d_C66SrrzrBn_8YTcAVH7lvZwDs7Bp5moVWVRc70ErWqU6Sruw7M9uUeow0&amp;xkcb=SoCk67M3jDe_E1QEE50JbzkdCdPP&amp;fccid=3a83feed94647eda&amp;vjs=3</v>
       </c>
       <c r="D51" t="str">
-        <v>El Segundo, CA 90245</v>
+        <v>$32.21 - $46.72 an hour</v>
       </c>
       <c r="E51" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F51" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=3152eec8dee0e33e&amp;bb=hXm0SXSCybqzMECR4SNEW6MMro5f7rkuyrFq5uuPwdRg7Weh0RHPEeuRAYNPokjfs897FhZg0-LdkRaET1ki6lWSwkbmBUpTQrjfV4mJIvtjFoW5Czzw9imRmCg0bwCc&amp;xkcb=SoDg67M3jDa8XHQHcp0DbzkdCdPP&amp;fccid=11619ce0d3c2c733&amp;vjs=3</v>
+        <v>Hybrid work in Anaheim Hills, CA</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
       </c>
       <c r="G51" t="str">
-        <v>machine learning</v>
+        <v>No</v>
       </c>
       <c r="H51" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Clinical Operations Business Intelligence Analyst (COBI) - Value Improvement Office - Full Time 8 Hour Days (Exempt) (Non-Union)</v>
+        <v>Boeing</v>
       </c>
       <c r="B52" t="str">
-        <v>USC</v>
+        <v>Senior Manufacturing Data Analyst - Millennium Space Systems</v>
       </c>
       <c r="C52" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=469d85e0672da7e5&amp;bb=ptVQyeMHI5dXXa3N0XapwaGydFHLTPU9n1yaN8WJ9hi2E1KJoCPAJNA2jPvTewm4l4qOc3Dnp_2pnWp3Jpu3d8-bkeK_WycrzB3EKGzCLNionnVldem4R5U0pHx5ITlX&amp;xkcb=SoAQ67M3jDe_E1QEE50IbzkdCdPP&amp;fccid=edae4285faf6c2f0&amp;vjs=3</v>
       </c>
       <c r="D52" t="str">
-        <v>Los Angeles, CA</v>
+        <v>$119,000 - $161,000 a year</v>
       </c>
       <c r="E52" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F52" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=9db9f1aed0caa4fd&amp;bb=WySx5_Ok87cfT1Bh4Wj579J1_X94bkH_P1I3qcsFgZAYZ8mBJxHzFOMy98ESjYrQpzOlkDs0wPg07n3_XnNQwhAHQdeA5v5n3PZpfJ7jXejsaTqMALPmgdhkIG27y2lv&amp;xkcb=SoBJ67M3jDa7yOwEE50LbzkdCdPP&amp;fccid=7455773bace145da&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
       </c>
       <c r="G52" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H52" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Workflow Systems Analyst (Anaheim, CA)</v>
+        <v>Boeing</v>
       </c>
       <c r="B53" t="str">
-        <v>Wescom Credit Union</v>
+        <v>Information Technology Analyst (Part-time) - Millennium Space Systems</v>
       </c>
       <c r="C53" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=e88c0d55cf43682a&amp;bb=ptVQyeMHI5dXXa3N0XapweAInEfggz1GitzLp92dbW9D6FhAZJqMaEytdZZFRrCbyj_JJrqeKeOHSJLIcNmbg3qPM98albSPJalaiSlAyvMD7Rtqtex3L62Iq-TObVB0&amp;xkcb=SoCe67M3jDe_E1QEE50PbzkdCdPP&amp;fccid=edae4285faf6c2f0&amp;vjs=3</v>
       </c>
       <c r="D53" t="str">
-        <v>Hybrid work in Anaheim Hills, CA</v>
+        <v>$21.15 an hour</v>
       </c>
       <c r="E53" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F53" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=5dfe0d094be4e7b7&amp;bb=WySx5_Ok87cfT1Bh4Wj5788VcV2Z6VqVgGroqUJwg8_4ZIpxsplk9Qk5aUpK5YHz1pEGPCpvv92unNYif7zorqcNMN8BAq_Tfbm74-Ku5WeFwUkd-VM0g9OBj1SWHMM9&amp;xkcb=SoD967M3jDa7yOwEE50KbzkdCdPP&amp;fccid=3a83feed94647eda&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
       </c>
       <c r="G53" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H53" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Senior Manufacturing Data Analyst - Millennium Space Systems</v>
+        <v>Applied Medical</v>
       </c>
       <c r="B54" t="str">
-        <v>Boeing</v>
+        <v>Senior Financial Systems Analyst</v>
       </c>
       <c r="C54" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=55a6d7436497a70c&amp;bb=ptVQyeMHI5dXXa3N0XapwRnT0Wss_enHu2YOCjKADwoMe4Ke3dLW08QMdf1CWRljgMIIqrCNZ_Rl11yvAtf7zUaQRX9X_c3va3GNzuZ7ZnFbI1v5HcZ4C_q6dQVUCO1u&amp;xkcb=SoDq67M3jDe_E1QEE50DbzkdCdPP&amp;fccid=dcdcc665244663ee&amp;vjs=3</v>
       </c>
       <c r="D54" t="str">
-        <v>El Segundo, CA 90245</v>
+        <v>$100,000 - $130,000 a year</v>
       </c>
       <c r="E54" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F54" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=469d85e0672da7e5&amp;bb=WySx5_Ok87cfT1Bh4Wj57-O0t5lYdguynKJmfA1LSP1af2JMQwme4Xc0sR2mk5RaUfefUiur0bLIFCPh08hU0nBa04Hv-4Np32nVZWBcHh_wtUbjV4K5LQzb2vQM2-c1&amp;xkcb=SoBg67M3jDa7yOwEE50JbzkdCdPP&amp;fccid=edae4285faf6c2f0&amp;vjs=3</v>
+        <v>Rancho Santa Margarita, CA 92688</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H54" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>BPO/BPaaS Manager</v>
+        <v>Disney</v>
       </c>
       <c r="B55" t="str">
-        <v>Deloitte</v>
+        <v>Sr Systems Analyst</v>
       </c>
       <c r="C55" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=5e858da1afef4101&amp;bb=ptVQyeMHI5dXXa3N0XapwbiS0JW81sii5EaEkh_NwIUECEfJuKa1L4Yp7C0eFlra8OZtpswYHQrauqNh0D5zL-p-dTVxSR8OpOWTc-KG5NMlScKbKCpv9G9a_vEQZcWu&amp;xkcb=SoBe67M3jDe_E1QEE50CbzkdCdPP&amp;fccid=4ed80f3a97849f22&amp;vjs=3</v>
       </c>
       <c r="D55" t="str">
-        <v>Inglewood, CA 90303</v>
+        <v>$105,100 - $140,900 a year</v>
       </c>
       <c r="E55" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F55" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=5970870bc64a39d7&amp;bb=WySx5_Ok87cfT1Bh4Wj571Ipj2fkJVjdyAG0TDnhmK5eGeMAEYYw_jvqG-Y_stnoGTvV86v79W21X6pSE3nASpfzxwYguL2KSL8g72kwsaMjNp0vsVVq5CK1KxtEOYtf&amp;xkcb=SoDU67M3jDa7yOwEE50IbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
+        <v>Anaheim, CA</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
       </c>
       <c r="G55" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H55" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Systems Engineering, Integration, and Test (SE&amp;I)</v>
+        <v>LA Clippers</v>
       </c>
       <c r="B56" t="str">
-        <v>KBR</v>
+        <v>Manager, Infrastructure</v>
       </c>
       <c r="C56" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=67ec630202297871&amp;bb=uEBEivTfP9WzoWJ_p90rTGXPuCHnKjrwAvmFPy8eljRNsm5xlwRZn1QDhuirVofF21_gy_zEivk2--xlq_jL1fOhOk-6gmCSAY9ngUIJB6aFghWdLdag_J_SAOFL7vvm7aQVgf-iIJZiW0T4vhMocPr517-tWjku&amp;xkcb=SoD367M3jDe7hhQHXB0LbzkdCdPP&amp;fccid=48ef1b46b21cbe88&amp;vjs=3</v>
       </c>
       <c r="D56" t="str">
-        <v>El Segundo, CA 90245</v>
+        <v>$150,000 - $175,000 a year</v>
       </c>
       <c r="E56" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F56" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=678dc8a1071b503d&amp;bb=WySx5_Ok87cfT1Bh4Wj570H4C9sH24F4kSoTF5FzkhV4CaysxCTGx09b4B-z9pg5eRarfF33gXp5yUYxmHfpQq7RpjvX0PwXOS3y2WaUhNApKlRqKVONHbnCW3v4gfSl&amp;xkcb=SoBa67M3jDa7yOwEE50PbzkdCdPP&amp;fccid=cbfa56f19cc95796&amp;vjs=3</v>
+        <v>Inglewood, CA</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
       </c>
       <c r="G56" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H56" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ERP - PTC Product Analyst</v>
+        <v>Boosted Commerce</v>
       </c>
       <c r="B57" t="str">
-        <v>Anduril Industries</v>
+        <v>Director of Technology</v>
       </c>
       <c r="C57" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=89ff55d3edb00bf3&amp;bb=uEBEivTfP9WzoWJ_p90rTHBoLKfSVARnINu95-aq8cx7Kbnli7k0GmiV6VXHswGRVwTc1yoyvQG6HtJxf3zO8EjDD3FTfGFkRS2D0g7FYS9d5l-cByZ5opZ3qSi9ymvsrgCAm9OnMrghydfNiVyue_CzCOb3keAo&amp;xkcb=SoBD67M3jDe7hhQHXB0KbzkdCdPP&amp;fccid=ac71512f1d9b439a&amp;cmp=Boosted-Commerce&amp;ti=Director+of+Technology&amp;vjs=3</v>
       </c>
       <c r="D57" t="str">
-        <v>Costa Mesa, CA 92626</v>
+        <v>$150,000 - $180,000 a year</v>
       </c>
       <c r="E57" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F57" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=32efe312935c5f42&amp;bb=WySx5_Ok87cfT1Bh4Wj57ygWl1aPK2O2w0zEyi3ryAx72EuVSqRhrazHmjZfk9J1poHOnT1OQ1nszuv1ecxRcZqVemVro8f4oBjy1li5DuzMGSSv1CQwRMlsio6pz4RD&amp;xkcb=SoAu67M3jDa7yOwEE50DbzkdCdPP&amp;fccid=3f7b0eacc8de6549&amp;vjs=3</v>
+        <v>Hybrid work in Santa Monica, CA 90405</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
       </c>
       <c r="G57" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H57" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Oracle Project Accountant System Analyst</v>
+        <v>Precision Castparts Corp.</v>
       </c>
       <c r="B58" t="str">
-        <v>Anduril Industries</v>
+        <v>IT Manager – Manufacturing Systems, ERP &amp; Infrastructure</v>
       </c>
       <c r="C58" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=39570582bbb28c43&amp;bb=uEBEivTfP9WzoWJ_p90rTO7pwRGUp946sws_CdwEpZGGF4lWu_6T8tNQrXCg39PHqdCZEfuy7lkqJ1DdReAOmUohP7Jz1NtiwGIxwM8bb3xjIytHT7bChzmgaf2VKjI7U0pgUj1NHR5ALRfDcqWVlc7B0iS3HqPa&amp;xkcb=SoDe67M3jDe7hhQHXB0JbzkdCdPP&amp;fccid=57efeaf4541a685c&amp;vjs=3</v>
       </c>
       <c r="D58" t="str">
-        <v>Costa Mesa, CA 92626</v>
+        <v>$141,000 - $170,000 a year</v>
       </c>
       <c r="E58" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F58" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=593966b425ff22c7&amp;bb=WySx5_Ok87cfT1Bh4Wj577p_UHDUBVKFCzQUE2RsOXe-8NzRU8KUPTYKj_Aad6zZtAm7NesiXF3x-I3lbju3IFrnnAIfGiuKToXpstEOVP3Kg2xsA_KwxEIHOZ10uuS4&amp;xkcb=SoA967M3jDa7yOwEE50HbzkdCdPP&amp;fccid=3f7b0eacc8de6549&amp;vjs=3</v>
+        <v>Santa Ana, CA</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
       </c>
       <c r="G58" t="str">
-        <v>systems analyst</v>
+        <v>No</v>
       </c>
       <c r="H58" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Cyberproof Chief Technology Officer</v>
+        <v>Mattel</v>
       </c>
       <c r="B59" t="str">
-        <v>UST Global</v>
+        <v>Sr Manager IT - Network Security</v>
       </c>
       <c r="C59" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=e98a926507171850&amp;bb=uEBEivTfP9WzoWJ_p90rTKL_OCyrCSpLJ1uykI8l6EEa1H6lX5zsPFiiG8nItIxYJPlc8I7uy6q9LGC0mEoNIXmSqByudWVnfXdKMxY-dqruOjTAOiIJPmFe5Ym5vW14TaByKADhuXMZeRQBaSdcNw%3D%3D&amp;xkcb=SoBq67M3jDe7hhQHXB0IbzkdCdPP&amp;fccid=c83b406ee927ab6a&amp;vjs=3</v>
       </c>
       <c r="D59" t="str">
-        <v>Aliso Viejo, CA 92656</v>
+        <v>$175,000 - $214,000 a year</v>
       </c>
       <c r="E59" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F59" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=2272e9e1dd1b991e&amp;bb=An1P8jzWpSXLl8wc8F5z7xpyTl04KssY9jb23ARbcgkdPpeVTlMfvdLIpmMCDm9p5B54q2V3eZxYY3ecs3VuzOffP_lcIF50T-vhpqkf2-1P6KVUcZUduR-RyO3TrEmK&amp;xkcb=SoCU67M3jDa7arSDl50LbzkdCdPP&amp;fccid=810178099fb1fcbc&amp;vjs=3</v>
+        <v>El Segundo, CA 90245</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
       </c>
       <c r="G59" t="str">
-        <v>technology manager</v>
+        <v>No</v>
       </c>
       <c r="H59" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Manager, Infrastructure</v>
+        <v>State Bar of California</v>
       </c>
       <c r="B60" t="str">
-        <v>LA Clippers</v>
+        <v>IT Manager I - Application Engineering</v>
       </c>
       <c r="C60" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=96ffa29c0a362f85&amp;bb=uEBEivTfP9WzoWJ_p90rTNDsr0PMS5Z4BTfrUpk3cVH94mlDat5R11E5nPiAQl_pYFBp5l1d7H2xuxaltviOc1H180QPyRCWPDh4UMYQwrLjtOdsiBIpyGwUPidrufOMKdl5xmRQbF4IIUEh0CaKZQ%3D%3D&amp;xkcb=SoDk67M3jDe7hhQHXB0PbzkdCdPP&amp;fccid=8ec0a97d6e779dde&amp;vjs=3</v>
       </c>
       <c r="D60" t="str">
-        <v>Inglewood, CA</v>
+        <v>$126,222 - $168,276 a year</v>
       </c>
       <c r="E60" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F60" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=67ec630202297871&amp;bb=An1P8jzWpSXLl8wc8F5z70GrB9bQ5i3G26m1kj_kudbCyOmXYC9o_VZeGUDV-NCJRUfynYu60Liu8olPEvPG8kuLICvXvh0LYKi-HHTCKZow7XhzjAKAdYXoZ6K_q61U&amp;xkcb=SoAg67M3jDa7arSDl50KbzkdCdPP&amp;fccid=48ef1b46b21cbe88&amp;vjs=3</v>
+        <v>Hybrid work in Los Angeles, CA 90017</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
       </c>
       <c r="G60" t="str">
-        <v>technology manager</v>
+        <v>No</v>
       </c>
       <c r="H60" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>IT Manager – Manufacturing Systems, ERP &amp; Infrastructure</v>
+        <v>Deloitte</v>
       </c>
       <c r="B61" t="str">
-        <v>Precision Castparts Corp.</v>
+        <v>Business Solutions Architect, Banking</v>
       </c>
       <c r="C61" t="str">
-        <v>Not listed</v>
+        <v>https://www.indeed.com/rc/clk?jk=037ea799b826614a&amp;bb=uEBEivTfP9WzoWJ_p90rTLrs3xbBjn87IDK54_ZpaWhxMO-4fbyURyZDHr6cR74mibk5YvW6lns8DRMh1kbLAESrDotWfHa0UtCPrd-0UaKS4O_i4xtSRU3X93DBFkHfd1iLHCUVVlfR3UbCidPPHA%3D%3D&amp;xkcb=SoAv67M3jDe7hhwHXB0IbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
       </c>
       <c r="D61" t="str">
-        <v>Santa Ana, CA</v>
+        <v>$130,800 - $241,000 a year</v>
       </c>
       <c r="E61" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F61" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=39570582bbb28c43&amp;bb=An1P8jzWpSXLl8wc8F5z77dqATIOsQumvo0Y_JOIwMec3MVtvzXfojhlxjvg2cGmw8iRtd3x2NeF3vjn1tKy98e3t1eckOnJ8rMw7yuaj5SElquuys8X-K43ryuRD9pf&amp;xkcb=SoC967M3jDa7arSDl50JbzkdCdPP&amp;fccid=57efeaf4541a685c&amp;vjs=3</v>
+        <v>Los Angeles, CA 90013 (Downtown area)</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
       </c>
       <c r="G61" t="str">
-        <v>technology manager</v>
+        <v>No</v>
       </c>
       <c r="H61" t="str">
-        <v>Los Angeles, CA</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>IT Director - Technology Services</v>
-      </c>
-      <c r="B62" t="str">
-        <v>State Bar of California</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Not listed</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Hybrid work in Los Angeles, CA 90017</v>
-      </c>
-      <c r="E62" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F62" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=a9e4a016d4aee690&amp;bb=An1P8jzWpSXLl8wc8F5z77KQd9qMSsE4_K-tuqOCCfdbjejiTXCwHLjtbhIqg5SWrcLGhi0B_eI5wNy7P_zQh4tab8hrNys1PZuJI1beMHh0XtD_v4yntMziwbkdak1g&amp;xkcb=SoAJ67M3jDa7arSDl50IbzkdCdPP&amp;fccid=8ec0a97d6e779dde&amp;vjs=3</v>
-      </c>
-      <c r="G62" t="str">
-        <v>technology manager</v>
-      </c>
-      <c r="H62" t="str">
-        <v>Los Angeles, CA</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Manager, Vulnerability Management</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Optimum</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Not listed</v>
-      </c>
-      <c r="D63" t="str">
-        <v>Norwalk, CA</v>
-      </c>
-      <c r="E63" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F63" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=c300dcc9574e0857&amp;bb=An1P8jzWpSXLl8wc8F5z74Y3AM6yAhhHWhoPKJgiFqF_gm6TvIZANBg6IQKvjp6atebb3nJ1R7QnvyJavU6dcFMyAIZxkaEKq9qhJqj-22bHKR2srEUWaRtagCo2yq1R&amp;xkcb=SoCH67M3jDa7arSDl50PbzkdCdPP&amp;fccid=ce93a27d3c480865&amp;vjs=3</v>
-      </c>
-      <c r="G63" t="str">
-        <v>technology manager</v>
-      </c>
-      <c r="H63" t="str">
-        <v>Los Angeles, CA</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Payments Delivery Lead, Banking</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Not listed</v>
-      </c>
-      <c r="D64" t="str">
-        <v>Los Angeles, CA 90013 (Downtown area)</v>
-      </c>
-      <c r="E64" t="str">
-        <v>Company Website</v>
-      </c>
-      <c r="F64" t="str">
-        <v>https://www.indeed.com/rc/clk?jk=4cff969ca4a3d69a&amp;bb=An1P8jzWpSXLl8wc8F5z7y5CdkhQme32N-KJPw28Nksk6C8dDSrRLXcDCX6YWcfJHXBKSPBaAmzsoc4Vv38eQgccI6uBhJO-qIz52kddy9Pw_n9cmpWaw0su68S2SL6I&amp;xkcb=SoBU67M3jDa7arSDl50GbzkdCdPP&amp;fccid=9e215d88a6b33622&amp;vjs=3</v>
-      </c>
-      <c r="G64" t="str">
-        <v>technology manager</v>
-      </c>
-      <c r="H64" t="str">
-        <v>Los Angeles, CA</v>
+        <v>08/05/2026</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I61"/>
   </ignoredErrors>
 </worksheet>
 </file>